--- a/outputs/dcf_models.xlsx
+++ b/outputs/dcf_models.xlsx
@@ -12,15 +12,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADBE" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCTY" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WDAY" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOCU" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZM" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRM" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAYC" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOW" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEAM" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOCU" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZM" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOW" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAYC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TWLO" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEAM" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VEEV" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TWLO" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZS" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OKTA" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MDB" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDOG" sheetId="17" state="visible" r:id="rId17"/>
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>230.94</v>
+        <v>234.87</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>368.5276403432546</v>
+        <v>369.961485385814</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.595772236698946</v>
+        <v>0.5751755668489547</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0.1066166666666667</v>
@@ -694,7 +694,7 @@
         <v>0.1917087560508048</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.0538970947265625</v>
+        <v>0.0577423095703125</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>0.1108543780254024</v>
@@ -712,7 +712,7 @@
         <v>3.360887535349141</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>3.133654760726173</v>
+        <v>3.196240666874038</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
@@ -733,16 +733,16 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>245.2</v>
+        <v>250.23</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>375.290185086368</v>
+        <v>376.475391259613</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.5305472474974227</v>
+        <v>0.5045174090221516</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.1091954730568281</v>
+        <v>0.1092714598079475</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0.1132166666666667</v>
@@ -754,7 +754,7 @@
         <v>0.0956654015764971</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>-0.0227325439453125</v>
+        <v>-0.0180633544921875</v>
       </c>
       <c r="L6" s="7" t="n">
         <v>0.06283270078824854</v>
@@ -766,13 +766,13 @@
         <v>0.3327864024569817</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>0.4857892246570725</v>
+        <v>0.4854573506595533</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>4.328151361438685</v>
+        <v>4.324002552256848</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>3.998773008877109</v>
+        <v>4.081135540241491</v>
       </c>
       <c r="R6" t="inlineStr"/>
     </row>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>166.32</v>
+        <v>170.91</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>240.1854844351954</v>
+        <v>244.9519902855507</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.4441166692832816</v>
+        <v>0.433222106872335</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.07940861755062996</v>
+        <v>0.07941165266091937</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0.07970333333333332</v>
@@ -814,7 +814,7 @@
         <v>0.1230298465241769</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.0272552490234375</v>
+        <v>0.0291778564453125</v>
       </c>
       <c r="L7" s="7" t="n">
         <v>0.07651492326208845</v>
@@ -826,13 +826,13 @@
         <v>0.25</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>0.690923186411373</v>
+        <v>0.6909072603619897</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>5.211641465906931</v>
+        <v>5.211321340880017</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>5.129153217228216</v>
+        <v>5.184206022372479</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>190.81</v>
+        <v>197.82</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>224.9967635437312</v>
+        <v>225.4372808167587</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.1791665192795511</v>
+        <v>0.1396081327305565</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.09746155185420442</v>
+        <v>0.09756998891341824</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>0.1007133333333333</v>
@@ -874,7 +874,7 @@
         <v>0.1333100384365797</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.08724060058593749</v>
+        <v>0.0967437744140625</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>0.08165501921828985</v>
@@ -886,85 +886,85 @@
         <v>0.25</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>0.6206082713072186</v>
+        <v>0.6201222364112385</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>3.816988979982258</v>
+        <v>3.810863434208214</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>4.601477513839215</v>
+        <v>4.780065394245846</v>
       </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DocuSign, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Maturing</t>
+          <t>Mature, profitable</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>74.65000000000001</v>
+        <v>229.17</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>86.87108647176464</v>
+        <v>253.667259410066</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.163711808061147</v>
+        <v>0.106895577126439</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.09301333333333334</v>
+        <v>0.1031208949725051</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.09301333333333334</v>
+        <v>0.1073866666666667</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.9093333333333333</v>
+        <v>1.170666666666667</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0.08126026885982759</v>
+        <v>0.0951246618345723</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.04027404785156251</v>
+        <v>0.0676849365234375</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0556301344299138</v>
+        <v>0.06256233091728615</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.1330668176663952</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>0.25</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>0.6195858472978144</v>
+        <v>0.5129395773726433</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4.086436732966567</v>
+        <v>3.675521120456186</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>4.172772737446687</v>
+        <v>4.693575265158591</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zoom Communications, Inc.</t>
+          <t>DocuSign, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -973,346 +973,346 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>94.19</v>
+        <v>82.17</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>99.29075218174428</v>
+        <v>87.16774073265853</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05415386115027365</v>
+        <v>0.06082196340098012</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.09920999999999999</v>
+        <v>0.09301333333333334</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.09920999999999999</v>
+        <v>0.09301333333333334</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>1.022</v>
+        <v>0.9093333333333333</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.0425252126851534</v>
+        <v>0.08126026885982759</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.0222564697265625</v>
+        <v>0.0652130126953125</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0362626063425767</v>
+        <v>0.0556301344299138</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.2348577061013407</v>
+        <v>0.1330668176663952</v>
       </c>
       <c r="N10" s="7" t="n">
         <v>0.25</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>0.5219968638873176</v>
+        <v>0.6195858472978144</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>3.720560612628233</v>
+        <v>4.086436732966567</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>4.053362204581053</v>
+        <v>4.612093448924637</v>
       </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Zoom Communications, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mature, profitable</t>
+          <t>Maturing</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>240.7</v>
+        <v>95.5</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>252.0023071272865</v>
+        <v>99.65141074225845</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.04695599138880979</v>
+        <v>0.04347026955244448</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.1033113515409423</v>
+        <v>0.09920999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.1073866666666667</v>
+        <v>0.09920999999999999</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>1.170666666666667</v>
+        <v>1.022</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0.0951246618345723</v>
+        <v>0.0425252126851534</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.08268127441406249</v>
+        <v>0.0262115478515625</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.06256233091728615</v>
+        <v>0.0362626063425767</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2348577061013407</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.25</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>0.5120587706097941</v>
+        <v>0.5219968638873176</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>3.66597243358701</v>
+        <v>3.720560612628233</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>4.923769620571291</v>
+        <v>4.13214383345701</v>
       </c>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>PAYC</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paycom Software, Inc.</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mature, profitable</t>
+          <t>Growth, profitable</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>251.64</v>
+        <v>105.12</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>244.8288102149409</v>
+        <v>104.3503592141274</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>-0.02706719831926208</v>
+        <v>-0.00732154476667235</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.09161999999999999</v>
+        <v>0.0969561177825697</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.09161999999999999</v>
+        <v>0.09763333333333332</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.8839999999999999</v>
+        <v>0.9933333333333332</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.0894753610875106</v>
+        <v>0.2088492352512745</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.09696350097656249</v>
+        <v>0.2110015869140625</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0597376805437553</v>
+        <v>0.1194246176256372</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.1410050202271287</v>
+        <v>0.1973941858713661</v>
       </c>
       <c r="N12" s="7" t="n">
         <v>0.25</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>0.6237751332153441</v>
+        <v>0.5983911312015848</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>4.178838039597534</v>
+        <v>3.845802422956988</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>5.347673613101331</v>
+        <v>7.856065682181051</v>
       </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>PAYC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Paycom Software, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Growth, profitable</t>
+          <t>Mature, profitable</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>141.97</v>
+        <v>264.2</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>104.1082226487905</v>
+        <v>245.6528149111778</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-0.2666885775248959</v>
+        <v>-0.07020130616511044</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.0971281825089242</v>
+        <v>0.09161999999999999</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.09763333333333332</v>
+        <v>0.09161999999999999</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.9933333333333332</v>
+        <v>0.8839999999999999</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.2088492352512745</v>
+        <v>0.0894753610875106</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.3017486572265625</v>
+        <v>0.1093231201171875</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.1194246176256372</v>
+        <v>0.0597376805437553</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.1973941858713661</v>
+        <v>0.1410050202271287</v>
       </c>
       <c r="N13" s="7" t="n">
         <v>0.25</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>0.5975935027020892</v>
+        <v>0.6237751332153441</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>3.835944760842695</v>
+        <v>4.178838039597534</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>10.69320613827384</v>
+        <v>5.623591628405713</v>
       </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Atlassian Corporation</t>
+          <t>Twilio Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Growth, profitable</t>
+          <t>Maturing</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>207.82</v>
+        <v>205.03</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>141.4740191013711</v>
+        <v>155.9086794421973</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>-0.3192473337437632</v>
+        <v>-0.2395811371887173</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.1052714204698487</v>
+        <v>0.1091442142513122</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.10636</v>
+        <v>0.11109</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>1.152</v>
+        <v>1.238</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0.2312227390552258</v>
+        <v>0.136648515175741</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.3370697021484375</v>
+        <v>0.2153961181640625</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.1306113695276129</v>
+        <v>0.0833242575878705</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>-0.0198653467725269</v>
+        <v>0.0680886166379198</v>
       </c>
       <c r="N14" s="7" t="n">
         <v>0.25</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>0.6958095785012923</v>
+        <v>0.6037153082419821</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3.420953110658328</v>
+        <v>3.253554317721091</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>8.883454913853628</v>
+        <v>5.922275313090807</v>
       </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zscaler, Inc.</t>
+          <t>Atlassian Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>High growth, unprofitable</t>
+          <t>Growth, profitable</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>207.38</v>
+        <v>191.72</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>139.7575856628418</v>
+        <v>142.2428072390134</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>-0.3260797296612896</v>
+        <v>-0.2580700644741631</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.09334825561837574</v>
+        <v>0.1051818319028545</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0.09565333333333334</v>
+        <v>0.10636</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.9573333333333334</v>
+        <v>1.152</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0.2429731886212083</v>
+        <v>0.2312227390552258</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.3486053466796875</v>
+        <v>0.3129547119140625</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.1364865943106041</v>
+        <v>0.1306113695276129</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.0068641291386864</v>
+        <v>-0.0198653467725269</v>
       </c>
       <c r="N15" s="7" t="n">
         <v>0.25</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>0.7225275327163128</v>
+        <v>0.6961189737682958</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4.064831738244513</v>
+        <v>3.425029604662015</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>11.6982158822047</v>
+        <v>8.191960082839509</v>
       </c>
       <c r="R15" t="inlineStr"/>
     </row>
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>310.36</v>
+        <v>312.96</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>197.5974096073511</v>
+        <v>198.2899815049556</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>-0.3633283618786213</v>
+        <v>-0.3664047114488892</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>0.09558</v>
@@ -1354,7 +1354,7 @@
         <v>0.1632637311788301</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.3220733642578125</v>
+        <v>0.3237213134765625</v>
       </c>
       <c r="L16" s="7" t="n">
         <v>0.09663186558941506</v>
@@ -1372,67 +1372,67 @@
         <v>4.426226880305591</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>13.83480677407914</v>
+        <v>13.96811173430613</v>
       </c>
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Twilio Inc.</t>
+          <t>Zscaler, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Maturing</t>
+          <t>High growth, unprofitable</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>244.37</v>
+        <v>237.83</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>154.6167574404823</v>
+        <v>139.4439977617566</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>-0.3672842106621832</v>
+        <v>-0.4136820512056655</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.1094493883159377</v>
+        <v>0.0936310120281309</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.11109</v>
+        <v>0.09565333333333334</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>1.238</v>
+        <v>0.9573333333333334</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.136648515175741</v>
+        <v>0.2429731886212083</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.2691741943359375</v>
+        <v>0.3874420166015625</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0833242575878705</v>
+        <v>0.1364865943106041</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.0680886166379198</v>
+        <v>0.0068641291386864</v>
       </c>
       <c r="N17" s="7" t="n">
         <v>0.25</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>0.602505398107525</v>
+        <v>0.721449442524995</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>3.241057048495175</v>
+        <v>4.046768891341234</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>7.114575450838921</v>
+        <v>13.37774189559688</v>
       </c>
       <c r="R17" t="inlineStr"/>
     </row>
@@ -1453,16 +1453,16 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>187.26</v>
+        <v>208.24</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>103.61134294969</v>
+        <v>103.8633934378699</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>-0.4466979443036956</v>
+        <v>-0.5012322635522961</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.08777830433721823</v>
+        <v>0.08782138315479542</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>0.08821</v>
@@ -1474,7 +1474,7 @@
         <v>0.1209440480418428</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.2848297119140625</v>
+        <v>0.3146026611328125</v>
       </c>
       <c r="L18" s="7" t="n">
         <v>0.0754720240209214</v>
@@ -1486,13 +1486,13 @@
         <v>0.25</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>0.6693679570361392</v>
+        <v>0.6691632823620656</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>4.456690153056809</v>
+        <v>4.453369773438984</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>11.13936460934935</v>
+        <v>12.40705484282382</v>
       </c>
       <c r="R18" t="inlineStr"/>
     </row>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>337.57</v>
+        <v>352.96</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>161.5431765829726</v>
+        <v>162.276496012086</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>-0.5214528050982832</v>
+        <v>-0.540241115106284</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0.1254266666666667</v>
@@ -1534,7 +1534,7 @@
         <v>0.2254084426782584</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.4687957763671874</v>
+        <v>0.4820892333984375</v>
       </c>
       <c r="L19" s="7" t="n">
         <v>0.1277042213391292</v>
@@ -1552,7 +1552,7 @@
         <v>2.698407153835406</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>10.22646096341891</v>
+        <v>10.73755837380588</v>
       </c>
       <c r="R19" t="inlineStr"/>
     </row>
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>247.11</v>
+        <v>235.27</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>72.51888335827871</v>
+        <v>72.86128834260121</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>-0.7065319762118947</v>
+        <v>-0.6903077810915068</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0.1160128636795396</v>
+        <v>0.1159750333628199</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>0.1167733333333333</v>
@@ -1594,7 +1594,7 @@
         <v>0.2767536858183308</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.6874786376953126</v>
+        <v>0.6688018798828124</v>
       </c>
       <c r="L20" s="7" t="n">
         <v>0.1533768429091654</v>
@@ -1606,13 +1606,13 @@
         <v>0.25</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>0.6169225123917587</v>
+        <v>0.617058152373396</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>2.993738250122382</v>
+        <v>2.995055540290799</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>24.87181460790544</v>
+        <v>23.63129893865413</v>
       </c>
       <c r="R20" t="inlineStr"/>
     </row>
@@ -1633,16 +1633,16 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>306.84</v>
+        <v>306.08</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>88.86755023366669</v>
+        <v>89.23124019187139</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>-0.7103782093805674</v>
+        <v>-0.7084708566653444</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.1095608828296811</v>
+        <v>0.1095576994337118</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0.11087</v>
@@ -1654,7 +1654,7 @@
         <v>0.2916598872820696</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.6651763916015625</v>
+        <v>0.6630889892578125</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>0.1608299436410348</v>
@@ -1666,13 +1666,13 @@
         <v>0.25</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>0.753720487359907</v>
+        <v>0.7537289714302291</v>
       </c>
       <c r="P21" s="9" t="n">
-        <v>3.236515116998385</v>
+        <v>3.23664462186405</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>23.17396364875435</v>
+        <v>23.11562095109607</v>
       </c>
       <c r="R21" t="inlineStr"/>
     </row>
@@ -1693,16 +1693,16 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>227.39</v>
+        <v>250.43</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>33.29202424079855</v>
+        <v>33.41186342074332</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>-0.8535906405699523</v>
+        <v>-0.8665820252336249</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.1050387884941039</v>
+        <v>0.1050557177229024</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>0.1052233333333333</v>
@@ -1714,7 +1714,7 @@
         <v>0.2221541930904092</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.8569976806640625</v>
+        <v>0.8904510498046874</v>
       </c>
       <c r="L22" s="7" t="n">
         <v>0.1260770965452046</v>
@@ -1726,13 +1726,13 @@
         <v>0.25</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>0.659639072440648</v>
+        <v>0.6595751071020113</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>3.431558600126291</v>
+        <v>3.430784593262598</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>48.16985200032507</v>
+        <v>53.14645484730876</v>
       </c>
       <c r="R22" t="inlineStr"/>
     </row>
@@ -1767,14 +1767,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOW · ServiceNow, Inc. — DCF</t>
+          <t>PAYC · Paycom Software, Inc. — DCF</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0.9933333333333332</v>
+        <v>0.8839999999999999</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Blume-adjusted from raw 0.99</t>
+          <t>Blume-adjusted from raw 0.83</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.09763333333333332</v>
+        <v>0.09161999999999999</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.01005608807715575</v>
+        <v>0</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.0971281825089242</v>
+        <v>0.09161999999999999</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0.2088492352512745</v>
+        <v>0.0894753610875106</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.1194246176256372</v>
+        <v>0.0597376805437553</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0.1973941858713661</v>
+        <v>0.1410050202271287</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
@@ -2076,37 +2076,37 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>13278</v>
+        <v>2051.7</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>15813.62413109978</v>
+        <v>2223.074038508921</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>18550.63652095141</v>
+        <v>2395.54076459586</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>21429.59262521752</v>
+        <v>2567.139943915669</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>24372.08015563395</v>
+        <v>2735.763087309073</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>27282.70650896191</v>
+        <v>2899.19122866214</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>30052.9841821159</v>
+        <v>3055.139143596574</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>32567.05967897639</v>
+        <v>3201.304969025869</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>34708.99021293918</v>
+        <v>3335.423871893457</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>36371.02755492018</v>
+        <v>3455.324141966337</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>37462.15838156779</v>
+        <v>3558.983866225327</v>
       </c>
     </row>
     <row r="21">
@@ -2116,31 +2116,31 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.1909643117261471</v>
+        <v>0.08352782497875955</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1730793882010196</v>
+        <v>0.07758028887000848</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.1551944646758922</v>
+        <v>0.07163275276125741</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1373095411507647</v>
+        <v>0.06568521665250636</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.1194246176256372</v>
+        <v>0.0597376805437553</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.1015396941005098</v>
+        <v>0.05379014443500424</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.08365477057538234</v>
+        <v>0.04784260832625318</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.0657698470502549</v>
+        <v>0.04189507221750212</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.04788492352512744</v>
+        <v>0.03594753610875106</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>0.03</v>
@@ -2153,34 +2153,34 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>0.1973941858713661</v>
+        <v>0.1410050202271287</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.2026547672842295</v>
+        <v>0.1519045182044158</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.2079153486970929</v>
+        <v>0.162804016181703</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.2131759301099563</v>
+        <v>0.1737035141589901</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.2184365115228196</v>
+        <v>0.1846030121362772</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.223697092935683</v>
+        <v>0.1955025101135643</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.2289576743485464</v>
+        <v>0.2064020080908515</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.2342182557614098</v>
+        <v>0.2173015060681386</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.2394788371742732</v>
+        <v>0.2282010040454258</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.2447394185871366</v>
+        <v>0.2391005020227129</v>
       </c>
       <c r="L22" s="7" t="n">
         <v>0.25</v>
@@ -2193,37 +2193,37 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>2620.999999999999</v>
+        <v>289.3</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>3204.706318208302</v>
+        <v>337.6949907524427</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>3856.962060806638</v>
+        <v>390.0036574031935</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4568.273339758203</v>
+        <v>445.9212295960644</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>5323.752167751219</v>
+        <v>505.030106408496</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>6103.062133472217</v>
+        <v>566.7991625026771</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>6880.861365570909</v>
+        <v>630.5868542352971</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>7627.799913287589</v>
+        <v>695.6483911527372</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>8312.068615687906</v>
+        <v>761.1470764831683</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>8901.42413720789</v>
+        <v>826.1697369953507</v>
       </c>
       <c r="L23" s="16" t="n">
-        <v>9365.539595391947</v>
+        <v>889.7459665563317</v>
       </c>
     </row>
     <row r="24">
@@ -2270,34 +2270,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9547096545761374</v>
+        <v>0.9571152984789053</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8701897096407617</v>
+        <v>0.8767843191576786</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.7931522710963478</v>
+        <v>0.8031955434653804</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.7229349165769845</v>
+        <v>0.7357830961922468</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.658933867621347</v>
+        <v>0.6740285962076975</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.600598797958585</v>
+        <v>0.6174571702677649</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5474281014139381</v>
+        <v>0.565633801384882</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.4989645787441844</v>
+        <v>0.5181599836801103</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4547915063152848</v>
+        <v>0.4746706579946413</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.4145290528179331</v>
+        <v>0.4348314046963607</v>
       </c>
     </row>
     <row r="26">
@@ -2307,34 +2307,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>3059.564062074613</v>
+        <v>323.2130418688553</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>3356.288695788763</v>
+        <v>341.9490912252636</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>3623.336374418117</v>
+        <v>358.1619443481616</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>3848.726329269768</v>
+        <v>371.5926153635431</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>4021.514335942238</v>
+        <v>382.0388438333781</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>4132.637065081555</v>
+        <v>389.3603746241781</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>4175.672024496426</v>
+        <v>393.482243915</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>4147.427815319472</v>
+        <v>394.3959567286822</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>4048.29209171201</v>
+        <v>392.1585326748428</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>3882.288257606672</v>
+        <v>386.8894884606109</v>
       </c>
     </row>
     <row r="28">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>38295.74705170964</v>
+        <v>3733.242133042515</v>
       </c>
     </row>
     <row r="30">
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>56871.07383428221</v>
+        <v>6189.658936597183</v>
       </c>
     </row>
     <row r="31">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>95166.82088599185</v>
+        <v>9922.901069639698</v>
       </c>
     </row>
     <row r="32">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>4793</v>
+        <v>370</v>
       </c>
     </row>
     <row r="33">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>99959.82088599185</v>
+        <v>10292.9010696397</v>
       </c>
     </row>
     <row r="34">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.076768010423101</v>
+        <v>1.075690043526794</v>
       </c>
     </row>
     <row r="35">
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>107633.5374576589</v>
+        <v>11071.97119961771</v>
       </c>
     </row>
     <row r="36">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>1033.86202087765</v>
+        <v>45.07162355791068</v>
       </c>
     </row>
     <row r="37">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>104.1082226487905</v>
+        <v>245.6528149111778</v>
       </c>
     </row>
     <row r="38">
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>141.97</v>
+        <v>264.2</v>
       </c>
     </row>
     <row r="39">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>-0.2666885775248959</v>
+        <v>-0.07020130616511044</v>
       </c>
     </row>
     <row r="40">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.3017486572265625</v>
+        <v>0.1093231201171875</v>
       </c>
     </row>
     <row r="41">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.5975935027020892</v>
+        <v>0.6237751332153441</v>
       </c>
     </row>
     <row r="42">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>3.835944760842695</v>
+        <v>4.178838039597534</v>
       </c>
     </row>
     <row r="44">
@@ -2515,108 +2515,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.0771281825089242</v>
-      </c>
-      <c r="B46" s="28" t="n">
-        <v>131.7910913546183</v>
-      </c>
-      <c r="C46" s="28" t="n">
-        <v>140.1824615067617</v>
+        <v>0.07161999999999999</v>
+      </c>
+      <c r="B46" s="26" t="n">
+        <v>317.0783410734656</v>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>340.7518380750617</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>150.3543735142067</v>
+        <v>370.1133449280746</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>162.9408003195047</v>
+        <v>407.4927400533467</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>178.9172198351307</v>
+        <v>456.6935757621961</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.08712818250892421</v>
+        <v>0.08162</v>
       </c>
       <c r="B47" s="28" t="n">
-        <v>111.1194668257836</v>
-      </c>
-      <c r="C47" s="28" t="n">
-        <v>116.6331530016999</v>
-      </c>
-      <c r="D47" s="28" t="n">
-        <v>123.1119821129887</v>
-      </c>
-      <c r="E47" s="28" t="n">
-        <v>130.8336761774494</v>
-      </c>
-      <c r="F47" s="28" t="n">
-        <v>140.1938153618759</v>
+        <v>262.6833786824337</v>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>277.7028981336105</v>
+      </c>
+      <c r="D47" s="26" t="n">
+        <v>295.6320494040777</v>
+      </c>
+      <c r="E47" s="26" t="n">
+        <v>317.4070074678669</v>
+      </c>
+      <c r="F47" s="26" t="n">
+        <v>344.4138151385253</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.0971281825089242</v>
+        <v>0.09161999999999999</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>95.92813342952714</v>
+        <v>223.7927922328513</v>
       </c>
       <c r="C48" s="28" t="n">
-        <v>99.73465192860381</v>
+        <v>233.9024784940227</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>104.1082226487905</v>
+        <v>245.6528149111778</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>109.1857525938521</v>
-      </c>
-      <c r="F48" s="28" t="n">
-        <v>115.1520785275255</v>
+        <v>259.4784491766471</v>
+      </c>
+      <c r="F48" s="26" t="n">
+        <v>275.9824318081507</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.1071281825089242</v>
+        <v>0.10162</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>84.32006257789948</v>
+        <v>194.6809798940113</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>87.04734648559338</v>
+        <v>201.78648462404</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>90.12823446108425</v>
+        <v>209.8841011566418</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>93.63626310036618</v>
+        <v>219.1972110144616</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>97.66687830585163</v>
+        <v>230.0216986486234</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1171281825089242</v>
+        <v>0.11162</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>75.18048489966995</v>
+        <v>172.1247596679313</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>77.19188066880123</v>
+        <v>177.2865973631289</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>79.43413122121981</v>
+        <v>183.0808582015756</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>81.94940018022193</v>
+        <v>189.6313525088875</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>84.79078455867024</v>
+        <v>197.0964648429115</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($141.97); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($264.20); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -2651,14 +2651,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEAM · Atlassian Corporation — DCF</t>
+          <t>TWLO · Twilio Inc. — DCF</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -2676,11 +2676,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>1.152</v>
+        <v>1.238</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Blume-adjusted from raw 1.23</t>
+          <t>Blume-adjusted from raw 1.36</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.10636</v>
+        <v>0.11109</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.01846301781124962</v>
+        <v>0.03055088316356977</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.1052714204698487</v>
+        <v>0.1091442142513122</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0.2312227390552258</v>
+        <v>0.136648515175741</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.1306113695276129</v>
+        <v>0.0833242575878705</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>-0.0198653467725269</v>
+        <v>0.0680886166379198</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
@@ -2960,37 +2960,37 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>5893.806</v>
+        <v>5067.22</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>7137.991188102112</v>
+        <v>5705.606940161936</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>8501.191834322753</v>
+        <v>6363.570755042533</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>9953.670763647877</v>
+        <v>7029.543638262548</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>11454.0238233864</v>
+        <v>7690.244182240691</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>12950.04956156081</v>
+        <v>8331.028069395337</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>14380.8888258789</v>
+        <v>8936.355620872569</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>15680.44404253289</v>
+        <v>9490.361006913281</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>16781.90974377701</v>
+        <v>9977.498419094491</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>17623.05722061235</v>
+        <v>10383.2319108238</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>18151.74893723072</v>
+        <v>10694.72886814851</v>
       </c>
     </row>
     <row r="21">
@@ -3000,34 +3000,34 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.2111004651497032</v>
+        <v>0.1259836636581669</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1909781912441806</v>
+        <v>0.1153188121405928</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.1708559173386581</v>
+        <v>0.1046539606230187</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1507336434331355</v>
+        <v>0.0939891091054446</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.1306113695276129</v>
+        <v>0.0833242575878705</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.1104890956220903</v>
+        <v>0.0726594060702964</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.09036682171656776</v>
+        <v>0.06199455455272231</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.07024454781104517</v>
+        <v>0.05132970303514819</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.05012227390552257</v>
+        <v>0.0406648515175741</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.02999999999999997</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="22">
@@ -3037,34 +3037,34 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>-0.0198653467725269</v>
+        <v>0.0680886166379198</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.007121187904725788</v>
+        <v>0.08627975497412782</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.03410772258197847</v>
+        <v>0.1044708933103358</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.06109425725923116</v>
+        <v>0.1226620316465439</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.08808079193648385</v>
+        <v>0.1408531699827519</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.1150673266137365</v>
+        <v>0.1590443083189599</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.1420538612909892</v>
+        <v>0.1772354466551679</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.1690403959682419</v>
+        <v>0.1954265849913759</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.1960269306454946</v>
+        <v>0.2136177233275839</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.2230134653227473</v>
+        <v>0.231808861663792</v>
       </c>
       <c r="L22" s="7" t="n">
         <v>0.25</v>
@@ -3077,37 +3077,37 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>-117.0824999999997</v>
+        <v>345.02</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>50.83097651275202</v>
+        <v>492.278368775855</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>289.9562927012612</v>
+        <v>664.8079214228218</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>608.1121223079913</v>
+        <v>862.2581042173217</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>1008.879489223227</v>
+        <v>1083.195271010017</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>1490.127582564193</v>
+        <v>1325.002596882821</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>2042.860786512538</v>
+        <v>1583.83897993477</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>2650.628469907619</v>
+        <v>1854.668841916378</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>3289.706257442325</v>
+        <v>2131.370496791533</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>3930.179060349824</v>
+        <v>2406.925169639224</v>
       </c>
       <c r="L23" s="16" t="n">
-        <v>4537.93723430768</v>
+        <v>2673.682217037128</v>
       </c>
     </row>
     <row r="24">
@@ -3154,34 +3154,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9511861758442426</v>
+        <v>0.9495240974971869</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8605905827546821</v>
+        <v>0.8560871393429474</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.7786237541443412</v>
+        <v>0.7718447505231032</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.704463844558063</v>
+        <v>0.6958921487447052</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6373672850950916</v>
+        <v>0.627413585900948</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.5766613279696927</v>
+        <v>0.5656735867521618</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.521737301164048</v>
+        <v>0.5100090497555355</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.4720445055407825</v>
+        <v>0.4598221252047</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4270846932241469</v>
+        <v>0.4145737941887804</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.3864070718870067</v>
+        <v>0.3737780794074859</v>
       </c>
     </row>
     <row r="26">
@@ -3191,34 +3191,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>48.34972216359311</v>
+        <v>467.4301738292811</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>249.5336549091655</v>
+        <v>569.1335116633944</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>473.4905436121309</v>
+        <v>665.5293913361427</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>710.7191236739693</v>
+        <v>753.7870846532639</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>949.7585717442514</v>
+        <v>831.324630638319</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>1178.038814007531</v>
+        <v>895.9358766175867</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>1382.931744278191</v>
+        <v>945.8978936769715</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>1552.88776366878</v>
+        <v>980.05131143328</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>1678.519318305471</v>
+        <v>997.8480999058071</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>1753.491039115852</v>
+        <v>999.3638040300865</v>
       </c>
     </row>
     <row r="28">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>9977.720295478937</v>
+        <v>8106.301777784134</v>
       </c>
     </row>
     <row r="30">
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>22823.18200223304</v>
+        <v>12349.45123609726</v>
       </c>
     </row>
     <row r="31">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>32800.90229771197</v>
+        <v>20455.75301388139</v>
       </c>
     </row>
     <row r="32">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>249.952</v>
+        <v>1478.055</v>
       </c>
     </row>
     <row r="33">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>33050.85429771197</v>
+        <v>21933.80801388139</v>
       </c>
     </row>
     <row r="34">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.083559520091333</v>
+        <v>1.091634858480082</v>
       </c>
     </row>
     <row r="35">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>35812.56782143738</v>
+        <v>23943.7094071627</v>
       </c>
     </row>
     <row r="36">
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>253.138831065345</v>
+        <v>153.5752178315369</v>
       </c>
     </row>
     <row r="37">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>141.4740191013711</v>
+        <v>155.9086794421973</v>
       </c>
     </row>
     <row r="38">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>207.82</v>
+        <v>205.03</v>
       </c>
     </row>
     <row r="39">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>-0.3192473337437632</v>
+        <v>-0.2395811371887173</v>
       </c>
     </row>
     <row r="40">
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.3370697021484375</v>
+        <v>0.2153961181640625</v>
       </c>
     </row>
     <row r="41">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.6958095785012923</v>
+        <v>0.6037153082419821</v>
       </c>
     </row>
     <row r="42">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>3.420953110658328</v>
+        <v>3.253554317721091</v>
       </c>
     </row>
     <row r="44">
@@ -3399,108 +3399,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.08527142046984872</v>
+        <v>0.08914421425131222</v>
       </c>
       <c r="B46" s="28" t="n">
-        <v>183.2575725568902</v>
+        <v>193.7655336679616</v>
       </c>
       <c r="C46" s="28" t="n">
-        <v>195.0782591194283</v>
+        <v>203.7002212210658</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>209.0376073016702</v>
+        <v>215.3146483190881</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>225.7737515345855</v>
+        <v>229.0741664963</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>246.2067411633863</v>
+        <v>245.6335093093987</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.09527142046984872</v>
+        <v>0.09914421425131223</v>
       </c>
       <c r="B47" s="28" t="n">
-        <v>152.4022892813264</v>
+        <v>166.3226156289476</v>
       </c>
       <c r="C47" s="28" t="n">
-        <v>160.4973078051281</v>
+        <v>173.2384965149728</v>
       </c>
       <c r="D47" s="28" t="n">
-        <v>169.8325350551274</v>
+        <v>181.1545884759099</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>180.7166269539479</v>
+        <v>190.304788930237</v>
       </c>
       <c r="F47" s="28" t="n">
-        <v>193.5699267736609</v>
+        <v>201.0020892268998</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.1052714204698487</v>
+        <v>0.1091442142513122</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>129.1798717658135</v>
+        <v>145.3048789759414</v>
       </c>
       <c r="C48" s="28" t="n">
-        <v>134.9440523919718</v>
+        <v>150.2917307960381</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>141.4740191013711</v>
+        <v>155.9086794421973</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>148.9332350938699</v>
+        <v>162.2831988176275</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>157.5352507893328</v>
+        <v>169.5796347184608</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.1152714204698487</v>
+        <v>0.1191442142513122</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>111.1565154950446</v>
+        <v>128.7468849752182</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>115.3869445340413</v>
+        <v>132.443468744653</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>120.1134869268074</v>
+        <v>136.5547270726647</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>125.4288493958971</v>
+        <v>141.1545820753963</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>131.4503713124784</v>
+        <v>146.3356362278378</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1252714204698487</v>
+        <v>0.1291442142513122</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>96.82594634710706</v>
+        <v>115.4055118007749</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>100.0066209486731</v>
+        <v>118.2074300442992</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>103.5211495628989</v>
+        <v>121.2919586513917</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>107.4250072245612</v>
+        <v>124.7041259383141</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>111.7866803700224</v>
+        <v>128.4990625743838</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($207.82); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($205.03); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -3535,14 +3535,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ZS · Zscaler, Inc. — DCF</t>
+          <t>TEAM · Atlassian Corporation — DCF</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -3560,11 +3560,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0.9573333333333334</v>
+        <v>1.152</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Blume-adjusted from raw 0.94</t>
+          <t>Blume-adjusted from raw 1.23</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.09565333333333334</v>
+        <v>0.10636</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.04777033120249243</v>
+        <v>0.01998249825552039</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.09334825561837574</v>
+        <v>0.1051818319028545</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0.2429731886212083</v>
+        <v>0.2312227390552258</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.1364865943106041</v>
+        <v>0.1306113695276129</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0.0068641291386864</v>
+        <v>-0.0198653467725269</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
@@ -3844,37 +3844,37 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>2956.201666666667</v>
+        <v>5893.806</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>3611.520242308264</v>
+        <v>7137.991188102112</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>4335.191434997056</v>
+        <v>8501.191834322753</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>5111.54285828324</v>
+        <v>9953.670763647877</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>5918.062092813266</v>
+        <v>11454.0238233864</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>6725.798232780035</v>
+        <v>12950.04956156081</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>7500.538058026657</v>
+        <v>14380.8888258789</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>8204.778251745256</v>
+        <v>15680.44404253289</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>8800.401156538439</v>
+        <v>16781.90974377701</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>9251.838140779968</v>
+        <v>17623.05722061235</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>9529.393285003369</v>
+        <v>18151.74893723072</v>
       </c>
     </row>
     <row r="21">
@@ -3884,31 +3884,31 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.2216758697590875</v>
+        <v>0.2111004651497032</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2003785508969667</v>
+        <v>0.1909781912441806</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.1790812320348458</v>
+        <v>0.1708559173386581</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.157783913172725</v>
+        <v>0.1507336434331355</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.1364865943106041</v>
+        <v>0.1306113695276129</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.1151892754484833</v>
+        <v>0.1104890956220903</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.09389195658636248</v>
+        <v>0.09036682171656776</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.07259463772424166</v>
+        <v>0.07024454781104517</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.05129731886212083</v>
+        <v>0.05012227390552257</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>0.02999999999999997</v>
@@ -3921,34 +3921,34 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>0.0068641291386864</v>
+        <v>-0.0198653467725269</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.03117771622481776</v>
+        <v>0.007121187904725788</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.05549130331094912</v>
+        <v>0.03410772258197847</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.07980489039708048</v>
+        <v>0.06109425725923116</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.1041184774832118</v>
+        <v>0.08808079193648385</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.1284320645693432</v>
+        <v>0.1150673266137365</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.1527456516554745</v>
+        <v>0.1420538612909892</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.1770592387416059</v>
+        <v>0.1690403959682419</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.2013728258277373</v>
+        <v>0.1960269306454946</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.2256864129138686</v>
+        <v>0.2230134653227473</v>
       </c>
       <c r="L22" s="7" t="n">
         <v>0.25</v>
@@ -3961,37 +3961,37 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>20.29174999999997</v>
+        <v>-117.0824999999997</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>112.5989532548721</v>
+        <v>50.83097651275202</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>240.5654228304504</v>
+        <v>289.9562927012612</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>407.9261175652734</v>
+        <v>608.1121223079913</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>616.1796147548276</v>
+        <v>1008.879489223227</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>863.8081529127799</v>
+        <v>1490.127582564193</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>1145.674573439969</v>
+        <v>2042.860786512538</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>1452.731791297699</v>
+        <v>2650.628469907619</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>1772.161649309833</v>
+        <v>3289.706257442325</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>2088.014162852347</v>
+        <v>3930.179060349824</v>
       </c>
       <c r="L23" s="16" t="n">
-        <v>2382.348321250842</v>
+        <v>4537.93723430768</v>
       </c>
     </row>
     <row r="24">
@@ -4038,34 +4038,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9563585432202709</v>
+        <v>0.9512247277264351</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8747062414064708</v>
+        <v>0.8606952270366743</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.8000252773182087</v>
+        <v>0.7787815562935616</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.7317204497351399</v>
+        <v>0.7046637338877432</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6692473747271802</v>
+        <v>0.6375998171038365</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.6121081469587816</v>
+        <v>0.5769184750404778</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5598473714238338</v>
+        <v>0.5220122683768375</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.5120485339844397</v>
+        <v>0.4723315687139547</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4683306817870537</v>
+        <v>0.4273790566215828</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.4283453870991684</v>
+        <v>0.3867047433142652</v>
       </c>
     </row>
     <row r="26">
@@ -4075,34 +4075,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>107.6849709029569</v>
+        <v>48.35168179341135</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>210.4240768163817</v>
+        <v>249.5639971772244</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>326.3512053304981</v>
+        <v>473.5865050119981</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>450.8712248260277</v>
+        <v>710.9207879187981</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>578.1013386048126</v>
+        <v>950.1050741043114</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>701.2767401661321</v>
+        <v>1178.564129674805</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>813.3080747418544</v>
+        <v>1383.660580200702</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>907.4327745125466</v>
+        <v>1553.832117185846</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>977.8810964696635</v>
+        <v>1679.676219166207</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>1020.467913871246</v>
+        <v>1754.841853369198</v>
       </c>
     </row>
     <row r="28">
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>6093.799416242119</v>
+        <v>9983.102945602501</v>
       </c>
     </row>
     <row r="30">
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>15868.01710522136</v>
+        <v>22868.90847939036</v>
       </c>
     </row>
     <row r="31">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>21961.81652146348</v>
+        <v>32852.01142499286</v>
       </c>
     </row>
     <row r="32">
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>-768.001</v>
+        <v>249.952</v>
       </c>
     </row>
     <row r="33">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>21193.81552146348</v>
+        <v>33101.96342499286</v>
       </c>
     </row>
     <row r="34">
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.075225533863918</v>
+        <v>1.087765598568086</v>
       </c>
     </row>
     <row r="35">
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>22788.13160867897</v>
+        <v>36007.17705876623</v>
       </c>
     </row>
     <row r="36">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>163.0547029028836</v>
+        <v>253.1388247861465</v>
       </c>
     </row>
     <row r="37">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>139.7575856628418</v>
+        <v>142.2428072390134</v>
       </c>
     </row>
     <row r="38">
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>207.38</v>
+        <v>191.72</v>
       </c>
     </row>
     <row r="39">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>-0.3260797296612896</v>
+        <v>-0.2580700644741631</v>
       </c>
     </row>
     <row r="40">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.3486053466796875</v>
+        <v>0.3129547119140625</v>
       </c>
     </row>
     <row r="41">
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.7225275327163128</v>
+        <v>0.6961189737682958</v>
       </c>
     </row>
     <row r="42">
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>4.064831738244513</v>
+        <v>3.425029604662015</v>
       </c>
     </row>
     <row r="44">
@@ -4283,108 +4283,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.07334825561837574</v>
+        <v>0.08518183190285451</v>
       </c>
       <c r="B46" s="28" t="n">
-        <v>188.2422352486948</v>
-      </c>
-      <c r="C46" s="28" t="n">
-        <v>204.3477487911886</v>
+        <v>184.2918838621262</v>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>196.2012996077747</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>224.168639876041</v>
+        <v>210.2689285433395</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>249.1581861618238</v>
+        <v>227.139888565501</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>281.6412417248994</v>
+        <v>247.7448627503544</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.08334825561837575</v>
+        <v>0.09518183190285452</v>
       </c>
       <c r="B47" s="28" t="n">
-        <v>151.1788032943678</v>
+        <v>153.2327359146145</v>
       </c>
       <c r="C47" s="28" t="n">
-        <v>161.517508948595</v>
+        <v>161.3852464734775</v>
       </c>
       <c r="D47" s="28" t="n">
-        <v>173.7941796842271</v>
+        <v>170.7884906065383</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>188.6100673116813</v>
-      </c>
-      <c r="F47" s="28" t="n">
-        <v>206.8438289495431</v>
+        <v>181.7542069734521</v>
+      </c>
+      <c r="F47" s="26" t="n">
+        <v>194.7071202109262</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.09334825561837574</v>
+        <v>0.1051818319028545</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>124.6142900059048</v>
+        <v>129.8642071300438</v>
       </c>
       <c r="C48" s="28" t="n">
-        <v>131.6320357808414</v>
+        <v>135.6675531655444</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>139.7575856628418</v>
+        <v>142.2428072390134</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>149.2757307125786</v>
+        <v>149.7549496630987</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>160.5780287658972</v>
+        <v>158.4195823141051</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.1033482556183757</v>
+        <v>0.1151818319028545</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>104.7394755547737</v>
+        <v>111.7318522945364</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>109.7031368917615</v>
+        <v>115.9900004504221</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>115.3435234344329</v>
+        <v>120.748037850383</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>121.8091521857958</v>
+        <v>126.0994811737363</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>129.2954292073041</v>
+        <v>132.1627245673869</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1133482556183757</v>
+        <v>0.1251818319028545</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>89.38018491414148</v>
+        <v>97.31740985797853</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>93.0039331823501</v>
+        <v>100.5183013367983</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>97.06245338925419</v>
+        <v>104.0554850906068</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>101.6389838792043</v>
+        <v>107.984896821955</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>106.8394597447285</v>
+        <v>112.3756054805435</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($207.38); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($191.72); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.075168394079346</v>
+        <v>1.078936893925932</v>
       </c>
     </row>
     <row r="35">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>31992.76701082689</v>
+        <v>32104.90268951319</v>
       </c>
     </row>
     <row r="36">
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>161.908838149246</v>
+        <v>161.9088490797546</v>
       </c>
     </row>
     <row r="37">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>197.5974096073511</v>
+        <v>198.2899815049556</v>
       </c>
     </row>
     <row r="38">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>310.36</v>
+        <v>312.96</v>
       </c>
     </row>
     <row r="39">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>-0.3633283618786213</v>
+        <v>-0.3664047114488892</v>
       </c>
     </row>
     <row r="40">
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.3220733642578125</v>
+        <v>0.3237213134765625</v>
       </c>
     </row>
     <row r="41">
@@ -5170,19 +5170,19 @@
         <v>0.07557999999999999</v>
       </c>
       <c r="B46" s="28" t="n">
-        <v>239.4563369976649</v>
+        <v>240.2956229480092</v>
       </c>
       <c r="C46" s="28" t="n">
-        <v>252.2891650673007</v>
+        <v>253.1734296239207</v>
       </c>
       <c r="D46" s="28" t="n">
-        <v>267.937444666036</v>
+        <v>268.8765558864736</v>
       </c>
       <c r="E46" s="28" t="n">
-        <v>287.4418799076337</v>
+        <v>288.4493534803603</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>312.4281687865551</v>
+        <v>313.5232184137318</v>
       </c>
     </row>
     <row r="47">
@@ -5190,19 +5190,19 @@
         <v>0.08558</v>
       </c>
       <c r="B47" s="28" t="n">
-        <v>208.1596914898618</v>
+        <v>208.8892838100566</v>
       </c>
       <c r="C47" s="28" t="n">
-        <v>216.5147024220094</v>
+        <v>217.2735787585649</v>
       </c>
       <c r="D47" s="28" t="n">
-        <v>226.3729538961051</v>
+        <v>227.1663830536922</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>238.1802467846127</v>
+        <v>239.0150600841155</v>
       </c>
       <c r="F47" s="28" t="n">
-        <v>252.5779944533985</v>
+        <v>253.4632713467511</v>
       </c>
     </row>
     <row r="48">
@@ -5210,19 +5210,19 @@
         <v>0.09558</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>185.2646847667735</v>
+        <v>185.9140309021453</v>
       </c>
       <c r="C48" s="28" t="n">
-        <v>190.9942122182121</v>
+        <v>191.6636401436606</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>197.5974096073511</v>
+        <v>198.2899815049556</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>205.2906032640931</v>
+        <v>206.0101395320306</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>214.3679627460856</v>
+        <v>215.1193148363771</v>
       </c>
     </row>
     <row r="49">
@@ -5230,19 +5230,19 @@
         <v>0.10558</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>167.815014597806</v>
+        <v>168.4032002594373</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>171.8990838490346</v>
+        <v>172.5015840282341</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>176.5235168540642</v>
+        <v>177.1422255065833</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>181.8031543086587</v>
+        <v>182.4403679028057</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>187.8878599935971</v>
+        <v>188.5464002649053</v>
       </c>
     </row>
     <row r="50">
@@ -5250,25 +5250,25 @@
         <v>0.11558</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>154.0927933715692</v>
+        <v>154.632883135522</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>157.092635406597</v>
+        <v>157.6432395102612</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>160.443008177197</v>
+        <v>161.0053552183422</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>164.2091631233493</v>
+        <v>164.784710403723</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>168.4736185386936</v>
+        <v>169.0641125837294</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($310.36); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($312.96); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -5303,14 +5303,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TWLO · Twilio Inc. — DCF</t>
+          <t>ZS · Zscaler, Inc. — DCF</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -5328,11 +5328,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>1.238</v>
+        <v>0.9573333333333334</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Blume-adjusted from raw 1.36</t>
+          <t>Blume-adjusted from raw 0.94</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.11109</v>
+        <v>0.09565333333333334</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.02575932931484221</v>
+        <v>0.04191049955517649</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.1094493883159377</v>
+        <v>0.0936310120281309</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0.136648515175741</v>
+        <v>0.2429731886212083</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.0833242575878705</v>
+        <v>0.1364865943106041</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0.0680886166379198</v>
+        <v>0.0068641291386864</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
@@ -5612,37 +5612,37 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>5067.22</v>
+        <v>2956.201666666667</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>5705.606940161936</v>
+        <v>3611.520242308264</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>6363.570755042533</v>
+        <v>4335.191434997056</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>7029.543638262548</v>
+        <v>5111.54285828324</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>7690.244182240691</v>
+        <v>5918.062092813266</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>8331.028069395337</v>
+        <v>6725.798232780035</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>8936.355620872569</v>
+        <v>7500.538058026657</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>9490.361006913281</v>
+        <v>8204.778251745256</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>9977.498419094491</v>
+        <v>8800.401156538439</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>10383.2319108238</v>
+        <v>9251.838140779968</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>10694.72886814851</v>
+        <v>9529.393285003369</v>
       </c>
     </row>
     <row r="21">
@@ -5652,34 +5652,34 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.1259836636581669</v>
+        <v>0.2216758697590875</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1153188121405928</v>
+        <v>0.2003785508969667</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.1046539606230187</v>
+        <v>0.1790812320348458</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0939891091054446</v>
+        <v>0.157783913172725</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.0833242575878705</v>
+        <v>0.1364865943106041</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.0726594060702964</v>
+        <v>0.1151892754484833</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.06199455455272231</v>
+        <v>0.09389195658636248</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.05132970303514819</v>
+        <v>0.07259463772424166</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.0406648515175741</v>
+        <v>0.05129731886212083</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.03</v>
+        <v>0.02999999999999997</v>
       </c>
     </row>
     <row r="22">
@@ -5689,34 +5689,34 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>0.0680886166379198</v>
+        <v>0.0068641291386864</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.08627975497412782</v>
+        <v>0.03117771622481776</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1044708933103358</v>
+        <v>0.05549130331094912</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.1226620316465439</v>
+        <v>0.07980489039708048</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.1408531699827519</v>
+        <v>0.1041184774832118</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.1590443083189599</v>
+        <v>0.1284320645693432</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.1772354466551679</v>
+        <v>0.1527456516554745</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.1954265849913759</v>
+        <v>0.1770592387416059</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.2136177233275839</v>
+        <v>0.2013728258277373</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.231808861663792</v>
+        <v>0.2256864129138686</v>
       </c>
       <c r="L22" s="7" t="n">
         <v>0.25</v>
@@ -5729,37 +5729,37 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>345.02</v>
+        <v>20.29174999999997</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>492.278368775855</v>
+        <v>112.5989532548721</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>664.8079214228218</v>
+        <v>240.5654228304504</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>862.2581042173217</v>
+        <v>407.9261175652734</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>1083.195271010017</v>
+        <v>616.1796147548276</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>1325.002596882821</v>
+        <v>863.8081529127799</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>1583.83897993477</v>
+        <v>1145.674573439969</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>1854.668841916378</v>
+        <v>1452.731791297699</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>2131.370496791533</v>
+        <v>1772.161649309833</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>2406.925169639224</v>
+        <v>2088.014162852347</v>
       </c>
       <c r="L23" s="16" t="n">
-        <v>2673.682217037128</v>
+        <v>2382.348321250842</v>
       </c>
     </row>
     <row r="24">
@@ -5806,34 +5806,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9493934966510775</v>
+        <v>0.9562349028030114</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8557339403216822</v>
+        <v>0.8743670326517906</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.771314085467768</v>
+        <v>0.7995082647028114</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.6952224171654787</v>
+        <v>0.7310585159981235</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6266373432507588</v>
+        <v>0.6684690795686022</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.5648183232602868</v>
+        <v>0.6112382258883926</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5090978725200248</v>
+        <v>0.5589071809099997</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.4588743550463332</v>
+        <v>0.5110564484391407</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4136054874417215</v>
+        <v>0.4673024473687795</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.3728024836442013</v>
+        <v>0.4272944368157321</v>
       </c>
     </row>
     <row r="26">
@@ -5843,34 +5843,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>467.3658818577976</v>
+        <v>107.6710491213935</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>568.8987021562185</v>
+        <v>210.3424749188842</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>665.071821091555</v>
+        <v>326.1403023815668</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>753.0616345737998</v>
+        <v>450.4633547509598</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>830.2961071110072</v>
+        <v>577.4290409014603</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>894.5812769610399</v>
+        <v>700.2800937148878</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>944.2079616488063</v>
+        <v>811.9422300925311</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>978.0312620799975</v>
+        <v>905.6746385563331</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>995.5174580243796</v>
+        <v>975.7341284415747</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>996.7553709867759</v>
+        <v>1017.964184227783</v>
       </c>
     </row>
     <row r="28">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>8093.787476491377</v>
+        <v>6083.641497107375</v>
       </c>
     </row>
     <row r="30">
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>12268.21854310433</v>
+        <v>15756.70788956824</v>
       </c>
     </row>
     <row r="31">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>20362.00601959571</v>
+        <v>21840.34938667561</v>
       </c>
     </row>
     <row r="32">
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>1478.055</v>
+        <v>-768.001</v>
       </c>
     </row>
     <row r="33">
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>21840.06101959571</v>
+        <v>21072.34838667561</v>
       </c>
     </row>
     <row r="34">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.087236017308952</v>
+        <v>1.078997002205288</v>
       </c>
     </row>
     <row r="35">
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>23745.30096072973</v>
+        <v>22737.00073864842</v>
       </c>
     </row>
     <row r="36">
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>153.5752097884356</v>
+        <v>163.0547108775176</v>
       </c>
     </row>
     <row r="37">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>154.6167574404823</v>
+        <v>139.4439977617566</v>
       </c>
     </row>
     <row r="38">
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>244.37</v>
+        <v>237.83</v>
       </c>
     </row>
     <row r="39">
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>-0.3672842106621832</v>
+        <v>-0.4136820512056655</v>
       </c>
     </row>
     <row r="40">
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.2691741943359375</v>
+        <v>0.3874420166015625</v>
       </c>
     </row>
     <row r="41">
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.602505398107525</v>
+        <v>0.721449442524995</v>
       </c>
     </row>
     <row r="42">
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>3.241057048495175</v>
+        <v>4.046768891341234</v>
       </c>
     </row>
     <row r="44">
@@ -6051,108 +6051,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.08944938831593768</v>
+        <v>0.0736310120281309</v>
       </c>
       <c r="B46" s="28" t="n">
-        <v>192.0288070720247</v>
+        <v>187.6524209949214</v>
       </c>
       <c r="C46" s="28" t="n">
-        <v>201.8086469970959</v>
+        <v>203.5978945813722</v>
       </c>
       <c r="D46" s="28" t="n">
-        <v>213.2335568214733</v>
-      </c>
-      <c r="E46" s="28" t="n">
-        <v>226.7567289363442</v>
-      </c>
-      <c r="F46" s="28" t="n">
-        <v>243.0146511816858</v>
+        <v>223.1979874042895</v>
+      </c>
+      <c r="E46" s="26" t="n">
+        <v>247.8717481934108</v>
+      </c>
+      <c r="F46" s="26" t="n">
+        <v>279.8821186475886</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.09944938831593769</v>
+        <v>0.0836310120281309</v>
       </c>
       <c r="B47" s="28" t="n">
-        <v>164.9313453960382</v>
+        <v>150.8341554128596</v>
       </c>
       <c r="C47" s="28" t="n">
-        <v>171.747722922377</v>
+        <v>161.0890948794037</v>
       </c>
       <c r="D47" s="28" t="n">
-        <v>179.545588938626</v>
+        <v>173.2561629966557</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>188.5533758276726</v>
+        <v>187.9251465809791</v>
       </c>
       <c r="F47" s="28" t="n">
-        <v>199.0763653359918</v>
+        <v>205.9561845624972</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.1094493883159377</v>
+        <v>0.0936310120281309</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>144.1580717193035</v>
+        <v>124.4082443800795</v>
       </c>
       <c r="C48" s="28" t="n">
-        <v>149.0778005634464</v>
+        <v>131.378418474914</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>154.6167574404823</v>
+        <v>139.4439977617566</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>160.8997038924936</v>
+        <v>148.8852277508201</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>168.087330227851</v>
+        <v>160.0868627055986</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.1194493883159377</v>
+        <v>0.1036310120281309</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>127.7802007679047</v>
+        <v>104.6165612523239</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>131.4297654855658</v>
+        <v>109.5515466606463</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>135.487333520675</v>
+        <v>115.1567639824505</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>140.0253749039072</v>
+        <v>121.5786991634504</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>145.1346027341874</v>
+        <v>129.0098804614475</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1294493883159377</v>
+        <v>0.1136310120281309</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>114.575838918819</v>
+        <v>89.30925906392051</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>117.3438147577521</v>
+        <v>92.91491993381925</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>120.3901206986401</v>
+        <v>96.95172001660781</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>123.7589597967253</v>
+        <v>101.5019053374427</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>127.504418473939</v>
+        <v>106.6700619716552</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($244.37); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($237.83); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.01057818335657345</v>
+        <v>0.009522588708762323</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.08777830433721823</v>
+        <v>0.08782138315479542</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -6690,34 +6690,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9588039260873156</v>
+        <v>0.9587849411009046</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8814332132423927</v>
+        <v>0.8813808553021162</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.8103059324937067</v>
+        <v>0.8102257125577178</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.7449182698927104</v>
+        <v>0.7448150267169587</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6848070667732135</v>
+        <v>0.6846850395208424</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.6295465390721001</v>
+        <v>0.6294094325809119</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5787452613845631</v>
+        <v>0.5785963048047088</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.5320433943910949</v>
+        <v>0.5318853938380207</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4891101360173462</v>
+        <v>0.4889455218240862</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.4496413782727173</v>
+        <v>0.4494722473703296</v>
       </c>
     </row>
     <row r="26">
@@ -6727,34 +6727,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>370.8573465588319</v>
+        <v>370.8500033247323</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>421.0453788717468</v>
+        <v>421.0203683905561</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>468.6480512155107</v>
+        <v>468.6016552616342</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>512.4561713512759</v>
+        <v>512.3851466433284</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>551.3392675282724</v>
+        <v>551.2410231917212</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>584.2939453972808</v>
+        <v>584.1666942923918</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>610.4873265833954</v>
+        <v>610.3302002788195</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>629.2929363070035</v>
+        <v>629.1060556257838</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>640.3168440175117</v>
+        <v>640.1013399153744</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>643.4124714120508</v>
+        <v>643.1704542464698</v>
       </c>
     </row>
     <row r="28">
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>5432.14973924288</v>
+        <v>5430.972941170811</v>
       </c>
     </row>
     <row r="30">
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>10997.44277861429</v>
+        <v>10984.8982473302</v>
       </c>
     </row>
     <row r="31">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>16429.59251785717</v>
+        <v>16415.87118850101</v>
       </c>
     </row>
     <row r="32">
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>16937.59251785717</v>
+        <v>16923.87118850101</v>
       </c>
     </row>
     <row r="34">
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.069421815935725</v>
+        <v>1.072892561680423</v>
       </c>
     </row>
     <row r="35">
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>18113.43094802617</v>
+        <v>18157.49551298035</v>
       </c>
     </row>
     <row r="36">
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>174.8209262843106</v>
+        <v>174.820934613907</v>
       </c>
     </row>
     <row r="37">
@@ -6851,7 +6851,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>103.61134294969</v>
+        <v>103.8633934378699</v>
       </c>
     </row>
     <row r="38">
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>187.26</v>
+        <v>208.24</v>
       </c>
     </row>
     <row r="39">
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>-0.4466979443036956</v>
+        <v>-0.5012322635522961</v>
       </c>
     </row>
     <row r="40">
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.2848297119140625</v>
+        <v>0.3146026611328125</v>
       </c>
     </row>
     <row r="41">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.6693679570361392</v>
+        <v>0.6691632823620656</v>
       </c>
     </row>
     <row r="42">
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>4.456690153056809</v>
+        <v>4.453369773438984</v>
       </c>
     </row>
     <row r="44">
@@ -6935,108 +6935,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.06777830433721822</v>
+        <v>0.06782138315479541</v>
       </c>
       <c r="B46" s="28" t="n">
-        <v>136.9294587402426</v>
+        <v>137.2386108694593</v>
       </c>
       <c r="C46" s="28" t="n">
-        <v>148.7971079602938</v>
+        <v>149.1177689206948</v>
       </c>
       <c r="D46" s="28" t="n">
-        <v>163.8061499527992</v>
+        <v>164.1377846192078</v>
       </c>
       <c r="E46" s="28" t="n">
-        <v>183.3941481469724</v>
+        <v>183.7340899968225</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>210.0336920209617</v>
+        <v>210.3740082920922</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.07777830433721823</v>
+        <v>0.07782138315479542</v>
       </c>
       <c r="B47" s="28" t="n">
-        <v>111.1377982854358</v>
+        <v>111.4068298095705</v>
       </c>
       <c r="C47" s="28" t="n">
-        <v>118.4519450860679</v>
+        <v>118.7306319181418</v>
       </c>
       <c r="D47" s="28" t="n">
-        <v>127.2969429501887</v>
+        <v>127.5859250931393</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>138.2095772017634</v>
+        <v>138.5091788342368</v>
       </c>
       <c r="F47" s="28" t="n">
-        <v>152.0108096694375</v>
+        <v>152.3205484584555</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.08777830433721823</v>
+        <v>0.08782138315479542</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>93.12896530926952</v>
+        <v>93.36524862391254</v>
       </c>
       <c r="C48" s="28" t="n">
-        <v>97.95271781325998</v>
+        <v>98.19654350488192</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>103.61134294969</v>
+        <v>103.8633934378699</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>110.3421179415369</v>
+        <v>110.6030759236104</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>118.4816442662778</v>
+        <v>118.7521033594802</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.09777830433721822</v>
+        <v>0.09782138315479541</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>79.88694767517005</v>
+        <v>80.09664411294122</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>83.22625689329887</v>
+        <v>83.44177384635137</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>87.05824725044153</v>
+        <v>87.28012998975309</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>91.50063803136098</v>
+        <v>91.72948129923445</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>96.71189713264373</v>
+        <v>96.94833189543643</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1077783043372182</v>
+        <v>0.1078213831547954</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>69.77148000551448</v>
+        <v>69.95942026525368</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>72.16903965148344</v>
+        <v>72.36148971962838</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>74.87485487931416</v>
+        <v>75.07222362546841</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>77.9524588225419</v>
+        <v>78.15520175249794</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>81.48413195108235</v>
+        <v>81.69275305153035</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($187.26); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($208.24); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.098359886903888</v>
+        <v>1.103345803285513</v>
       </c>
     </row>
     <row r="35">
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>13013.32789313709</v>
+        <v>13072.4008486369</v>
       </c>
     </row>
     <row r="36">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>80.55634517285304</v>
+        <v>80.5563416137806</v>
       </c>
     </row>
     <row r="37">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>161.5431765829726</v>
+        <v>162.276496012086</v>
       </c>
     </row>
     <row r="38">
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>337.57</v>
+        <v>352.96</v>
       </c>
     </row>
     <row r="39">
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>-0.5214528050982832</v>
+        <v>-0.540241115106284</v>
       </c>
     </row>
     <row r="40">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.4687957763671874</v>
+        <v>0.4820892333984375</v>
       </c>
     </row>
     <row r="41">
@@ -7822,19 +7822,19 @@
         <v>0.1054266666666667</v>
       </c>
       <c r="B46" s="28" t="n">
-        <v>194.1968112476363</v>
+        <v>195.0783606746813</v>
       </c>
       <c r="C46" s="28" t="n">
-        <v>201.5470478027806</v>
+        <v>202.4619633638121</v>
       </c>
       <c r="D46" s="28" t="n">
-        <v>209.8717721458617</v>
+        <v>210.8244774930787</v>
       </c>
       <c r="E46" s="28" t="n">
-        <v>219.3785379992249</v>
+        <v>220.3743989674701</v>
       </c>
       <c r="F46" s="28" t="n">
-        <v>230.3383453015433</v>
+        <v>231.3839579201159</v>
       </c>
     </row>
     <row r="47">
@@ -7842,19 +7842,19 @@
         <v>0.1154266666666667</v>
       </c>
       <c r="B47" s="28" t="n">
-        <v>171.2455227170369</v>
+        <v>172.0228855968152</v>
       </c>
       <c r="C47" s="28" t="n">
-        <v>176.6422291812353</v>
+        <v>177.444090215545</v>
       </c>
       <c r="D47" s="28" t="n">
-        <v>182.6706712234185</v>
+        <v>183.4998981531521</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>189.4486708802631</v>
+        <v>190.3086662952031</v>
       </c>
       <c r="F47" s="28" t="n">
-        <v>197.1252916689149</v>
+        <v>198.0201348273085</v>
       </c>
     </row>
     <row r="48">
@@ -7862,19 +7862,19 @@
         <v>0.1254266666666667</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>153.000002945047</v>
+        <v>153.6945409452725</v>
       </c>
       <c r="C48" s="28" t="n">
-        <v>157.0589178233418</v>
+        <v>157.7718811213999</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>161.5431765829726</v>
+        <v>162.276496012086</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>166.5233353823738</v>
+        <v>167.2792620629039</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>172.0864689124681</v>
+        <v>172.8676492371983</v>
       </c>
     </row>
     <row r="49">
@@ -7882,19 +7882,19 @@
         <v>0.1354266666666667</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>138.2106821093627</v>
+        <v>138.8380845205673</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>141.3242070869193</v>
+        <v>141.965743232568</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>144.7330581974174</v>
+        <v>145.3900686998489</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>148.4813461550839</v>
+        <v>149.1553718756349</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>152.6224266191428</v>
+        <v>153.3152506252423</v>
       </c>
     </row>
     <row r="50">
@@ -7902,25 +7902,25 @@
         <v>0.1454266666666666</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>126.0288714955898</v>
+        <v>126.6009750164679</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>128.4568572053273</v>
+        <v>129.0399824798456</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>131.0951916828021</v>
+        <v>131.6902935816122</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>133.9724480219174</v>
+        <v>134.580611122201</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>137.122619784624</v>
+        <v>137.7450829761123</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($337.57); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($352.96); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.01096198809043353</v>
+        <v>0.01150730305372016</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.1160128636795396</v>
+        <v>0.1159750333628199</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -8458,34 +8458,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9465976015707752</v>
+        <v>0.9466136457395637</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8481959593635906</v>
+        <v>0.8482390890834614</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.7600234611696627</v>
+        <v>0.760087872689609</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.681016756978799</v>
+        <v>0.6810975603989997</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6102230351838949</v>
+        <v>0.6103161271866597</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.5467885317844499</v>
+        <v>0.546890484948902</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.4899482340926304</v>
+        <v>0.490056200720666</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.4390166547697767</v>
+        <v>0.4391282834025028</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.3933795649293155</v>
+        <v>0.3934929279548996</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.3524865866082646</v>
+        <v>0.3526001175574411</v>
       </c>
     </row>
     <row r="26">
@@ -8495,34 +8495,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>276.5346227847179</v>
+        <v>276.5393098536017</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>394.4356615340666</v>
+        <v>394.4557181016572</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>522.3997495686232</v>
+        <v>522.4440226254542</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>654.1661236971435</v>
+        <v>654.2437412588737</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>782.2328674291326</v>
+        <v>782.3522002305165</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>898.4989313068959</v>
+        <v>898.6664637330144</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>995.0675659581512</v>
+        <v>995.2868423679604</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>1065.108349229184</v>
+        <v>1065.379174008695</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>1103.652210694651</v>
+        <v>1103.970258109797</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>1108.193197366875</v>
+        <v>1108.550130737812</v>
       </c>
     </row>
     <row r="28">
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>7800.28927956944</v>
+        <v>7801.887861027382</v>
       </c>
     </row>
     <row r="30">
@@ -8549,7 +8549,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>12561.88164378823</v>
+        <v>12571.66992426535</v>
       </c>
     </row>
     <row r="31">
@@ -8559,7 +8559,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>20362.17092335767</v>
+        <v>20373.55778529273</v>
       </c>
     </row>
     <row r="32">
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>23853.55792335767</v>
+        <v>23864.94478529274</v>
       </c>
     </row>
     <row r="34">
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.091649252444623</v>
+        <v>1.096280318342964</v>
       </c>
     </row>
     <row r="35">
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>26039.71867517792</v>
+        <v>26162.66926645799</v>
       </c>
     </row>
     <row r="36">
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>359.0750087329529</v>
+        <v>359.0750295745314</v>
       </c>
     </row>
     <row r="37">
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>72.51888335827871</v>
+        <v>72.86128834260121</v>
       </c>
     </row>
     <row r="38">
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>247.11</v>
+        <v>235.27</v>
       </c>
     </row>
     <row r="39">
@@ -8639,7 +8639,7 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>-0.7065319762118947</v>
+        <v>-0.6903077810915068</v>
       </c>
     </row>
     <row r="40">
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.6874786376953126</v>
+        <v>0.6688018798828124</v>
       </c>
     </row>
     <row r="41">
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.6169225123917587</v>
+        <v>0.617058152373396</v>
       </c>
     </row>
     <row r="42">
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>2.993738250122382</v>
+        <v>2.995055540290799</v>
       </c>
     </row>
     <row r="44">
@@ -8703,108 +8703,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.09601286367953964</v>
+        <v>0.0959750333628199</v>
       </c>
       <c r="B46" s="28" t="n">
-        <v>88.37408830296727</v>
+        <v>88.79807604826561</v>
       </c>
       <c r="C46" s="28" t="n">
-        <v>92.25358912042206</v>
+        <v>92.69926376808424</v>
       </c>
       <c r="D46" s="28" t="n">
-        <v>96.72077854903723</v>
+        <v>97.1917642195486</v>
       </c>
       <c r="E46" s="28" t="n">
-        <v>101.9201397131209</v>
+        <v>102.4210417096958</v>
       </c>
       <c r="F46" s="28" t="n">
-        <v>108.0477450023095</v>
+        <v>108.5845352558213</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.1060128636795396</v>
+        <v>0.1059750333628199</v>
       </c>
       <c r="B47" s="28" t="n">
-        <v>77.04284566141895</v>
+        <v>77.40743906432716</v>
       </c>
       <c r="C47" s="28" t="n">
-        <v>79.81222110301883</v>
+        <v>80.19194343677631</v>
       </c>
       <c r="D47" s="28" t="n">
-        <v>82.94592638400947</v>
+        <v>83.34295036265664</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>86.52091865423239</v>
+        <v>86.93791719620936</v>
       </c>
       <c r="F47" s="28" t="n">
-        <v>90.63747086761695</v>
+        <v>91.07778209957931</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.1160128636795396</v>
+        <v>0.1159750333628199</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>68.20910246073854</v>
+        <v>68.52829158171643</v>
       </c>
       <c r="C48" s="28" t="n">
-        <v>70.24560907003524</v>
+        <v>70.57571892143702</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>72.51888335827871</v>
+        <v>72.86128834260121</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>75.07276422984648</v>
+        <v>75.42911382791833</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>77.96262519056532</v>
+        <v>78.33492211780423</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.1260128636795396</v>
+        <v>0.1259750333628199</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>61.15558029848751</v>
+        <v>61.43908983334016</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>62.68919200132297</v>
+        <v>62.98080053267316</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>64.38253351994167</v>
+        <v>64.68314787315271</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>66.26193022352645</v>
+        <v>66.57261768861837</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>68.35982874453553</v>
+        <v>68.68185709783248</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1360128636795396</v>
+        <v>0.1359750333628199</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>55.41327667945944</v>
+        <v>55.66812262153294</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>56.59091556008578</v>
+        <v>56.851901079727</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>57.8796389676037</v>
+        <v>58.14738306097082</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>59.29594250309487</v>
+        <v>59.57116229927905</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>60.8597578907706</v>
+        <v>61.14329045588626</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($247.11); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($235.27); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.02062576288512577</v>
+        <v>0.02067591880082171</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.1095608828296811</v>
+        <v>0.1095576994337118</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -9342,34 +9342,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9493457954265763</v>
+        <v>0.9493471572941981</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8556049605907944</v>
+        <v>0.8556086427760533</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.7711203358294046</v>
+        <v>0.7711258668321015</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.6949779392572301</v>
+        <v>0.6949849180674995</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6263540379008748</v>
+        <v>0.6263621246756262</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.5645062362900738</v>
+        <v>0.5645151441834025</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5087654449843526</v>
+        <v>0.5087749329949365</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.4585286421479304</v>
+        <v>0.4585385088622262</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4132523498652532</v>
+        <v>0.4132624279893258</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.3724467546218352</v>
+        <v>0.3724569062070803</v>
       </c>
     </row>
     <row r="26">
@@ -9379,34 +9379,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>-390.5920833363289</v>
+        <v>-390.592643653459</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>-216.4895482942421</v>
+        <v>-216.4904799796111</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>3.601671207899863</v>
+        <v>3.601697041550253</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>260.9287704964064</v>
+        <v>260.9313906837249</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>541.9397520296232</v>
+        <v>541.9467489426122</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>829.2400323828318</v>
+        <v>829.253117768391</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>1103.221431613463</v>
+        <v>1103.242005684919</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>1344.180809976218</v>
+        <v>1344.209734337305</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>1534.629703358127</v>
+        <v>1534.667128888947</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>1661.429262209939</v>
+        <v>1661.474546913255</v>
       </c>
     </row>
     <row r="28">
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>6672.089801643937</v>
+        <v>6672.243246627633</v>
       </c>
     </row>
     <row r="30">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>20419.44424485375</v>
+        <v>20420.84718052069</v>
       </c>
     </row>
     <row r="31">
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>27091.53404649769</v>
+        <v>27093.09042714833</v>
       </c>
     </row>
     <row r="32">
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>28841.39304649769</v>
+        <v>28842.94942714833</v>
       </c>
     </row>
     <row r="34">
@@ -9473,7 +9473,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.08706508903582</v>
+        <v>1.091454954236817</v>
       </c>
     </row>
     <row r="35">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>31352.47150000808</v>
+        <v>31480.78004706301</v>
       </c>
     </row>
     <row r="36">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>352.7999974970669</v>
+        <v>352.7999832723471</v>
       </c>
     </row>
     <row r="37">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>88.86755023366669</v>
+        <v>89.23124019187139</v>
       </c>
     </row>
     <row r="38">
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>306.84</v>
+        <v>306.08</v>
       </c>
     </row>
     <row r="39">
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>-0.7103782093805674</v>
+        <v>-0.7084708566653444</v>
       </c>
     </row>
     <row r="40">
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.6651763916015625</v>
+        <v>0.6630889892578125</v>
       </c>
     </row>
     <row r="41">
@@ -9543,7 +9543,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.753720487359907</v>
+        <v>0.7537289714302291</v>
       </c>
     </row>
     <row r="42">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>3.236515116998385</v>
+        <v>3.23664462186405</v>
       </c>
     </row>
     <row r="44">
@@ -9587,108 +9587,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.08956088282968105</v>
+        <v>0.08955769943371183</v>
       </c>
       <c r="B46" s="28" t="n">
-        <v>114.6536596834185</v>
+        <v>115.1236608659695</v>
       </c>
       <c r="C46" s="28" t="n">
-        <v>121.7252414727713</v>
+        <v>122.2246617159555</v>
       </c>
       <c r="D46" s="28" t="n">
-        <v>129.9841095234064</v>
+        <v>130.5179518782392</v>
       </c>
       <c r="E46" s="28" t="n">
-        <v>139.7566752311004</v>
+        <v>140.3313373246653</v>
       </c>
       <c r="F46" s="28" t="n">
-        <v>151.5010713723397</v>
+        <v>152.1249166781052</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.09956088282968106</v>
+        <v>0.09955769943371184</v>
       </c>
       <c r="B47" s="28" t="n">
-        <v>95.70733326102102</v>
+        <v>96.099067232205</v>
       </c>
       <c r="C47" s="28" t="n">
-        <v>100.638281840719</v>
+        <v>101.0504670381661</v>
       </c>
       <c r="D47" s="28" t="n">
-        <v>106.2780984478358</v>
+        <v>106.7137074953092</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>112.7914806507011</v>
+        <v>113.2541849833285</v>
       </c>
       <c r="F47" s="28" t="n">
-        <v>120.3984299555671</v>
+        <v>120.8928374428808</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.1095608828296811</v>
+        <v>0.1095576994337118</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>81.29980610442645</v>
+        <v>81.63216479031605</v>
       </c>
       <c r="C48" s="28" t="n">
-        <v>84.85994161746389</v>
+        <v>85.20703118817137</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>88.86755023366669</v>
+        <v>89.23124019187139</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>93.41265364125461</v>
+        <v>93.79519345193459</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>98.61115637655321</v>
+        <v>99.01528590251438</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.1195608828296811</v>
+        <v>0.1195576994337118</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>70.0401967829175</v>
+        <v>70.3262402682109</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>72.68190556618823</v>
+        <v>72.97885908983763</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>75.61857669237097</v>
+        <v>75.92766895236871</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>78.90253264197464</v>
+        <v>79.22521226936691</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>82.59924871097442</v>
+        <v>82.93724008509619</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1295608828296811</v>
+        <v>0.1295576994337118</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>61.04749858766851</v>
+        <v>61.29660760987296</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>63.05152332710999</v>
+        <v>63.30889599752258</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>65.25683442345027</v>
+        <v>65.52330721435523</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>67.69536152098975</v>
+        <v>67.97190467197996</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>70.40616452967413</v>
+        <v>70.69391217397913</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($306.84); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($306.08); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9730,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.003191528896571895</v>
+        <v>0.00289875385538089</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.1050387884941039</v>
+        <v>0.1050557177229024</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -10226,34 +10226,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9512862920922804</v>
+        <v>0.9512790053081329</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8608623534280181</v>
+        <v>0.8608425711495846</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.779033607138046</v>
+        <v>0.779003770889899</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.7049830424501905</v>
+        <v>0.7049452424852641</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6379713090532405</v>
+        <v>0.6379273290743086</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.5773293351291664</v>
+        <v>0.5772806916820747</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5224516470737867</v>
+        <v>0.5223996242213286</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.4727903242073156</v>
+        <v>0.472736004025023</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4278495281162144</v>
+        <v>0.4277938174910775</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.3871805520051184</v>
+        <v>0.3871242061645517</v>
       </c>
     </row>
     <row r="26">
@@ -10263,34 +10263,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>290.0551119272085</v>
+        <v>290.052890126044</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>437.60141372468</v>
+        <v>437.5913578162358</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>594.8732852846839</v>
+        <v>594.8505022021659</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>755.1358969317034</v>
+        <v>755.0954078579244</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>910.74407901787</v>
+        <v>910.6812948380187</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>1053.71094270909</v>
+        <v>1053.622161264301</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>1176.364211486911</v>
+        <v>1176.247075629164</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>1272.018611106049</v>
+        <v>1271.872465385002</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>1335.584257932454</v>
+        <v>1335.410350450868</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>1364.034354771972</v>
+        <v>1363.83584877294</v>
       </c>
     </row>
     <row r="28">
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>9190.122164892622</v>
+        <v>9189.259354342665</v>
       </c>
     </row>
     <row r="30">
@@ -10317,7 +10317,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>17810.98583769987</v>
+        <v>17804.240668866</v>
       </c>
     </row>
     <row r="31">
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>27001.1080025925</v>
+        <v>26993.50002320866</v>
       </c>
     </row>
     <row r="32">
@@ -10347,7 +10347,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>31485.7620025925</v>
+        <v>31478.15402320866</v>
       </c>
     </row>
     <row r="34">
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.082675538576347</v>
+        <v>1.086835363382458</v>
       </c>
     </row>
     <row r="35">
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>34088.86433364353</v>
+        <v>34211.57096642298</v>
       </c>
     </row>
     <row r="36">
@@ -10377,7 +10377,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>1023.934864611461</v>
+        <v>1023.934838222258</v>
       </c>
     </row>
     <row r="37">
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>33.29202424079855</v>
+        <v>33.41186342074332</v>
       </c>
     </row>
     <row r="38">
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>227.39</v>
+        <v>250.43</v>
       </c>
     </row>
     <row r="39">
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>-0.8535906405699523</v>
+        <v>-0.8665820252336249</v>
       </c>
     </row>
     <row r="40">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.8569976806640625</v>
+        <v>0.8904510498046874</v>
       </c>
     </row>
     <row r="41">
@@ -10427,7 +10427,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.659639072440648</v>
+        <v>0.6595751071020113</v>
       </c>
     </row>
     <row r="42">
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>3.431558600126291</v>
+        <v>3.430784593262598</v>
       </c>
     </row>
     <row r="44">
@@ -10471,108 +10471,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.08503878849410389</v>
+        <v>0.08505571772290237</v>
       </c>
       <c r="B46" s="28" t="n">
-        <v>41.45128650277787</v>
+        <v>41.59869473417746</v>
       </c>
       <c r="C46" s="28" t="n">
-        <v>43.73949732167581</v>
+        <v>43.89412988145074</v>
       </c>
       <c r="D46" s="28" t="n">
-        <v>46.443453268965</v>
+        <v>46.60649450348385</v>
       </c>
       <c r="E46" s="28" t="n">
-        <v>49.68778120140081</v>
+        <v>49.86072821568725</v>
       </c>
       <c r="F46" s="28" t="n">
-        <v>53.65244998689058</v>
+        <v>53.83723068237311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.0950387884941039</v>
+        <v>0.09505571772290237</v>
       </c>
       <c r="B47" s="28" t="n">
-        <v>35.44354179506002</v>
+        <v>35.57094263963748</v>
       </c>
       <c r="C47" s="28" t="n">
-        <v>37.00891467676394</v>
+        <v>37.1413773885265</v>
       </c>
       <c r="D47" s="28" t="n">
-        <v>38.81497052903791</v>
+        <v>38.95321055770169</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>40.92184122078044</v>
+        <v>41.06673576185262</v>
       </c>
       <c r="F47" s="28" t="n">
-        <v>43.41150934491343</v>
+        <v>43.56414937788266</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.1050387884941039</v>
+        <v>0.1050557177229024</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>30.9160748495783</v>
+        <v>31.02812643318426</v>
       </c>
       <c r="C48" s="28" t="n">
-        <v>32.0298371090708</v>
+        <v>32.14555499139885</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>33.29202424079855</v>
+        <v>33.41186342074332</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>34.73442396027458</v>
+        <v>34.8589291773274</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>36.39859898536026</v>
+        <v>36.52842976473571</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.1150387884941039</v>
+        <v>0.1150557177229024</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>27.39640748214769</v>
+        <v>27.49636288899386</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>28.21330478116426</v>
+        <v>28.31598669049778</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>29.12626380842066</v>
+        <v>29.23197365528418</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>30.15328740917116</v>
+        <v>30.26237930131417</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>31.31717670583187</v>
+        <v>31.43007037706107</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1250387884941039</v>
+        <v>0.1250557177229024</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>24.5924682687325</v>
+        <v>24.68268318910128</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>25.20634642461269</v>
+        <v>25.2986330103973</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>25.8848169606786</v>
+        <v>25.97938165032846</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>26.63864063592078</v>
+        <v>26.73572223013243</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>27.48110899773378</v>
+        <v>27.58098576538873</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($227.39); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($250.43); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -10614,7 +10614,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -11241,7 +11241,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.083759102919477</v>
+        <v>1.087975629488946</v>
       </c>
     </row>
     <row r="35">
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>18377.07362527825</v>
+        <v>18448.57237347915</v>
       </c>
     </row>
     <row r="36">
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>49.86620164544903</v>
+        <v>49.86619716438882</v>
       </c>
     </row>
     <row r="37">
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>368.5276403432546</v>
+        <v>369.961485385814</v>
       </c>
     </row>
     <row r="38">
@@ -11281,7 +11281,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>230.94</v>
+        <v>234.87</v>
       </c>
     </row>
     <row r="39">
@@ -11291,7 +11291,7 @@
         </is>
       </c>
       <c r="B39" s="22" t="n">
-        <v>0.595772236698946</v>
+        <v>0.5751755668489547</v>
       </c>
     </row>
     <row r="40">
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.0538970947265625</v>
+        <v>0.0577423095703125</v>
       </c>
     </row>
     <row r="41">
@@ -11358,19 +11358,19 @@
         <v>0.08661666666666666</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>462.4561088858996</v>
+        <v>464.2554051300286</v>
       </c>
       <c r="C46" s="26" t="n">
-        <v>488.3248374872436</v>
+        <v>490.2247822152362</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>518.7626674017483</v>
+        <v>520.7810377965064</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>555.0973968799282</v>
+        <v>557.2571362414387</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>599.2264909226087</v>
+        <v>601.5579250928636</v>
       </c>
     </row>
     <row r="47">
@@ -11378,19 +11378,19 @@
         <v>0.09661666666666667</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>393.5570127155364</v>
+        <v>395.0882405255347</v>
       </c>
       <c r="C47" s="26" t="n">
-        <v>411.3772098859058</v>
+        <v>412.9777714407118</v>
       </c>
       <c r="D47" s="26" t="n">
-        <v>431.8724429087199</v>
+        <v>433.5527460759556</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>455.6939241905787</v>
+        <v>457.4669105356912</v>
       </c>
       <c r="F47" s="26" t="n">
-        <v>483.7229087898102</v>
+        <v>485.6049486121005</v>
       </c>
     </row>
     <row r="48">
@@ -11398,19 +11398,19 @@
         <v>0.1066166666666667</v>
       </c>
       <c r="B48" s="26" t="n">
-        <v>341.3711366476103</v>
+        <v>342.6993228088957</v>
       </c>
       <c r="C48" s="26" t="n">
-        <v>354.11755766955</v>
+        <v>355.495336834431</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>368.5276403432546</v>
+        <v>369.961485385814</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>384.949836027018</v>
+        <v>386.4475755547975</v>
       </c>
       <c r="F48" s="26" t="n">
-        <v>403.8372099470232</v>
+        <v>405.4084353263305</v>
       </c>
     </row>
     <row r="49">
@@ -11418,19 +11418,19 @@
         <v>0.1166166666666667</v>
       </c>
       <c r="B49" s="26" t="n">
-        <v>300.6468006385083</v>
+        <v>301.8165390175763</v>
       </c>
       <c r="C49" s="26" t="n">
-        <v>310.0349491558457</v>
+        <v>311.2412143750657</v>
       </c>
       <c r="D49" s="26" t="n">
-        <v>320.5069708905013</v>
+        <v>321.7539800181994</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>332.262066556297</v>
+        <v>333.5548116988826</v>
       </c>
       <c r="F49" s="26" t="n">
-        <v>345.5514361832581</v>
+        <v>346.8958868010168</v>
       </c>
     </row>
     <row r="50">
@@ -11438,25 +11438,25 @@
         <v>0.1266166666666667</v>
       </c>
       <c r="B50" s="26" t="n">
-        <v>268.1083514218238</v>
+        <v>269.1514911716588</v>
       </c>
       <c r="C50" s="26" t="n">
-        <v>275.1872852119263</v>
+        <v>276.2579672489887</v>
       </c>
       <c r="D50" s="26" t="n">
-        <v>282.9989014712477</v>
+        <v>284.0999764721523</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>291.663159126893</v>
+        <v>292.7979444971893</v>
       </c>
       <c r="F50" s="26" t="n">
-        <v>301.3277159153819</v>
+        <v>302.5001035584053</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($230.94); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($234.87); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.0610968894885577</v>
+        <v>0.05994236807372744</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.1091954730568281</v>
+        <v>0.1092714598079475</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -11994,34 +11994,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9495021572555655</v>
+        <v>0.9494696355409288</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8560277970111398</v>
+        <v>0.8559398397442897</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.7717555812340414</v>
+        <v>0.7716234220003118</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.6957795987998064</v>
+        <v>0.6956127962887516</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6272831215965116</v>
+        <v>0.6270897805386482</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.5655298248448347</v>
+        <v>0.5653167896767295</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5098558717394446</v>
+        <v>0.5096288962258211</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.4596627773230398</v>
+        <v>0.459426672993151</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4144109748809709</v>
+        <v>0.4141697408069017</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.3736140156963471</v>
+        <v>0.37337095184853</v>
       </c>
     </row>
     <row r="26">
@@ -12031,34 +12031,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>8179.744592399846</v>
+        <v>8179.464425243402</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>7983.117598317743</v>
+        <v>7982.297329154353</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>7743.956381866114</v>
+        <v>7742.630268565026</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>7466.115105810103</v>
+        <v>7464.325218970043</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>7154.042254099194</v>
+        <v>7151.837236859312</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>6812.661003656369</v>
+        <v>6810.094673255393</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>6447.238420691396</v>
+        <v>6444.368265941589</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>6063.248396397305</v>
+        <v>6060.134028059894</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>5666.23337818831</v>
+        <v>5662.934989281404</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>5261.66985107678</v>
+        <v>5258.246741487162</v>
       </c>
     </row>
     <row r="28">
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>68778.02698250316</v>
+        <v>68756.33317681758</v>
       </c>
     </row>
     <row r="30">
@@ -12085,7 +12085,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>64976.51547459541</v>
+        <v>64869.77782671365</v>
       </c>
     </row>
     <row r="31">
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>133754.5424570986</v>
+        <v>133626.1110035312</v>
       </c>
     </row>
     <row r="32">
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>134139.5424570986</v>
+        <v>134011.1110035312</v>
       </c>
     </row>
     <row r="34">
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.088887964720676</v>
+        <v>1.093373625073815</v>
       </c>
     </row>
     <row r="35">
@@ -12135,7 +12135,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>146062.9333746728</v>
+        <v>146524.2142381003</v>
       </c>
     </row>
     <row r="36">
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>389.1999822512235</v>
+        <v>389.1999786436479</v>
       </c>
     </row>
     <row r="37">
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>375.290185086368</v>
+        <v>376.475391259613</v>
       </c>
     </row>
     <row r="38">
@@ -12165,7 +12165,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>245.2</v>
+        <v>250.23</v>
       </c>
     </row>
     <row r="39">
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="B39" s="22" t="n">
-        <v>0.5305472474974227</v>
+        <v>0.5045174090221516</v>
       </c>
     </row>
     <row r="40">
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>-0.0227325439453125</v>
+        <v>-0.0180633544921875</v>
       </c>
     </row>
     <row r="41">
@@ -12195,7 +12195,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.4857892246570725</v>
+        <v>0.4854573506595533</v>
       </c>
     </row>
     <row r="42">
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>4.328151361438685</v>
+        <v>4.324002552256848</v>
       </c>
     </row>
     <row r="44">
@@ -12239,108 +12239,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.08919547305682808</v>
+        <v>0.0892714598079475</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>457.7571283477529</v>
+        <v>459.1280212568501</v>
       </c>
       <c r="C46" s="26" t="n">
-        <v>478.3134918860271</v>
+        <v>479.7091219495689</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>502.3424796769261</v>
+        <v>503.7625684828332</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>530.8052303700703</v>
+        <v>532.248076843508</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>565.0536253358624</v>
+        <v>566.5149256539496</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.09919547305682809</v>
+        <v>0.09927145980794751</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>398.8513152987513</v>
+        <v>400.1029087208078</v>
       </c>
       <c r="C47" s="26" t="n">
-        <v>413.1642496439185</v>
+        <v>414.4374181603369</v>
       </c>
       <c r="D47" s="26" t="n">
-        <v>429.5456624187964</v>
+        <v>430.841251601305</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>448.478877056771</v>
+        <v>449.7973583981274</v>
       </c>
       <c r="F47" s="26" t="n">
-        <v>470.6105144220709</v>
+        <v>471.9516497610535</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.1091954730568281</v>
+        <v>0.1092714598079475</v>
       </c>
       <c r="B48" s="26" t="n">
-        <v>353.342190017385</v>
+        <v>354.4904062364726</v>
       </c>
       <c r="C48" s="26" t="n">
-        <v>363.6644899524649</v>
+        <v>364.8306914327416</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>375.290185086368</v>
+        <v>376.475391259613</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>388.482781091029</v>
+        <v>389.687947684023</v>
       </c>
       <c r="F48" s="26" t="n">
-        <v>403.5819463294642</v>
+        <v>404.8078634251041</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.1191954730568281</v>
+        <v>0.1192714598079475</v>
       </c>
       <c r="B49" s="26" t="n">
-        <v>317.1585655154392</v>
+        <v>318.2175711307566</v>
       </c>
       <c r="C49" s="26" t="n">
-        <v>324.8111024895715</v>
+        <v>325.884875697871</v>
       </c>
       <c r="D49" s="26" t="n">
-        <v>333.3215907376721</v>
+        <v>334.4110554960625</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>342.842880153474</v>
+        <v>343.9489870566683</v>
       </c>
       <c r="F49" s="26" t="n">
-        <v>353.5664212950746</v>
+        <v>354.6901172947948</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1291954730568281</v>
+        <v>0.1292714598079475</v>
       </c>
       <c r="B50" s="26" t="n">
-        <v>287.72285789494</v>
+        <v>288.7046746770343</v>
       </c>
       <c r="C50" s="26" t="n">
-        <v>293.5238888679808</v>
+        <v>294.5177888764601</v>
       </c>
       <c r="D50" s="26" t="n">
-        <v>299.9097278765374</v>
+        <v>300.9164806639128</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>306.973501694626</v>
+        <v>307.9939241966433</v>
       </c>
       <c r="F50" s="26" t="n">
-        <v>314.829218598614</v>
+        <v>315.8641679757186</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($245.20); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($250.23); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.009123386111960671</v>
+        <v>0.009029429545370291</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.07940861755062996</v>
+        <v>0.07941165266091937</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -12878,34 +12878,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9625140096845416</v>
+        <v>0.9625126564759574</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8917049521696956</v>
+        <v>0.8917011912028302</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.8261050890932599</v>
+        <v>0.8260992819603592</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.7653311967879589</v>
+        <v>0.7653236649093927</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.7090282441181833</v>
+        <v>0.7090192726961485</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.6568673184461827</v>
+        <v>0.6568571600540948</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.6085437041782484</v>
+        <v>0.6085325820180267</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.5637751026660713</v>
+        <v>0.5637632135227539</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.5222999830642239</v>
+        <v>0.5222874999848195</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.4838760545097513</v>
+        <v>0.483863129230909</v>
       </c>
     </row>
     <row r="26">
@@ -12915,34 +12915,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>281.0342183072927</v>
+        <v>281.0338231983251</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>306.8821939759502</v>
+        <v>306.8808996310435</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>330.9657503271334</v>
+        <v>330.9634237925034</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>352.6638947257065</v>
+        <v>352.6604240431564</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>371.3985106291314</v>
+        <v>371.3938112778579</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>386.6595966820659</v>
+        <v>386.6536170273056</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>398.0282214910489</v>
+        <v>398.0209468555185</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>405.1957662717559</v>
+        <v>405.1872213209164</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>407.9782219888464</v>
+        <v>407.968471223567</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>406.324602751189</v>
+        <v>406.3137490237891</v>
       </c>
     </row>
     <row r="28">
@@ -12959,7 +12959,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>3647.13097715012</v>
+        <v>3647.076387393982</v>
       </c>
     </row>
     <row r="30">
@@ -12969,7 +12969,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>8152.948539666545</v>
+        <v>8152.218515699522</v>
       </c>
     </row>
     <row r="31">
@@ -12979,7 +12979,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>11800.07951681667</v>
+        <v>11799.2949030935</v>
       </c>
     </row>
     <row r="32">
@@ -12999,7 +12999,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>11990.74651681667</v>
+        <v>11989.9619030935</v>
       </c>
     </row>
     <row r="34">
@@ -13009,7 +13009,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.062778969772234</v>
+        <v>1.065907476188481</v>
       </c>
     </row>
     <row r="35">
@@ -13019,7 +13019,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>12743.51322994241</v>
+        <v>12780.19003172244</v>
       </c>
     </row>
     <row r="36">
@@ -13029,7 +13029,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>53.05696661856662</v>
+        <v>52.17426491135686</v>
       </c>
     </row>
     <row r="37">
@@ -13039,7 +13039,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>240.1854844351954</v>
+        <v>244.9519902855507</v>
       </c>
     </row>
     <row r="38">
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>166.32</v>
+        <v>170.91</v>
       </c>
     </row>
     <row r="39">
@@ -13059,7 +13059,7 @@
         </is>
       </c>
       <c r="B39" s="22" t="n">
-        <v>0.4441166692832816</v>
+        <v>0.433222106872335</v>
       </c>
     </row>
     <row r="40">
@@ -13069,7 +13069,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.0272552490234375</v>
+        <v>0.0291778564453125</v>
       </c>
     </row>
     <row r="41">
@@ -13079,7 +13079,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.690923186411373</v>
+        <v>0.6909072603619897</v>
       </c>
     </row>
     <row r="42">
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>5.211641465906931</v>
+        <v>5.211321340880017</v>
       </c>
     </row>
     <row r="44">
@@ -13123,108 +13123,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.05940861755062996</v>
+        <v>0.05941165266091937</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>329.0964883202115</v>
+        <v>335.6217702358578</v>
       </c>
       <c r="C46" s="26" t="n">
-        <v>365.9925143714102</v>
+        <v>373.2452772779599</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>415.4345317422207</v>
+        <v>423.6608254460252</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>485.1325170179132</v>
+        <v>494.7286206652602</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>590.7413470994642</v>
+        <v>602.4073095887252</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.06940861755062996</v>
+        <v>0.06941165266091938</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>258.1122946179609</v>
+        <v>263.234328502642</v>
       </c>
       <c r="C47" s="26" t="n">
-        <v>279.0653063962496</v>
+        <v>284.601234523384</v>
       </c>
       <c r="D47" s="26" t="n">
-        <v>305.3351785671594</v>
+        <v>311.3896097234506</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>339.2397289207236</v>
+        <v>345.9626663115429</v>
       </c>
       <c r="F47" s="26" t="n">
-        <v>384.6730600118365</v>
+        <v>392.2906069201551</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.07940861755062996</v>
+        <v>0.07941165266091937</v>
       </c>
       <c r="B48" s="26" t="n">
-        <v>211.3773956908396</v>
+        <v>215.5743285707089</v>
       </c>
       <c r="C48" s="26" t="n">
-        <v>224.457748612966</v>
+        <v>228.9133721914732</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>240.1854844351954</v>
+        <v>244.9519902855507</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>259.4548157156257</v>
+        <v>264.6019619621062</v>
       </c>
       <c r="F48" s="26" t="n">
-        <v>283.6137707580857</v>
+        <v>289.2377615220076</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.08940861755062995</v>
+        <v>0.08941165266091937</v>
       </c>
       <c r="B49" s="26" t="n">
-        <v>178.38111546968</v>
+        <v>181.9243091427332</v>
       </c>
       <c r="C49" s="26" t="n">
-        <v>187.0854364757089</v>
+        <v>190.8009201473268</v>
       </c>
       <c r="D49" s="26" t="n">
-        <v>197.2549188278356</v>
+        <v>201.1716170100021</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>209.2934952334298</v>
+        <v>213.4482837073565</v>
       </c>
       <c r="F49" s="26" t="n">
-        <v>223.7686053860486</v>
+        <v>228.209519536936</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.09940861755062996</v>
+        <v>0.09941165266091938</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>153.9101982086841</v>
+        <v>156.9682439055397</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>159.9759750119526</v>
-      </c>
-      <c r="D50" s="26" t="n">
-        <v>166.9156745379788</v>
+        <v>163.1541590198646</v>
+      </c>
+      <c r="D50" s="28" t="n">
+        <v>170.2312667332974</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>174.9328229815464</v>
+        <v>178.407105409385</v>
       </c>
       <c r="F50" s="26" t="n">
-        <v>184.2994639354784</v>
+        <v>187.9590779430427</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($166.32); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($170.91); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -13266,7 +13266,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -13340,7 +13340,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.06099377539944165</v>
+        <v>0.05895981780508471</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.09746155185420442</v>
+        <v>0.09756998891341824</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -13762,34 +13762,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9545646403360358</v>
+        <v>0.954517484919874</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8697932412513781</v>
+        <v>0.8696643444714038</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.7925500804851235</v>
+        <v>0.792354340275249</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.7221666026897061</v>
+        <v>0.7219169148927539</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6580336244760259</v>
+        <v>0.6577411210080947</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.5995960618066777</v>
+        <v>0.5992703223046859</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5463481256301295</v>
+        <v>0.5459973654144431</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.4978289441730809</v>
+        <v>0.4974601810632362</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4536185740010475</v>
+        <v>0.4532377762585473</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.4133343653220846</v>
+        <v>0.4129465827571028</v>
       </c>
     </row>
     <row r="26">
@@ -13799,34 +13799,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>1325.522822090105</v>
+        <v>1325.457341369716</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>1480.125949027318</v>
+        <v>1479.906605556091</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>1623.538069844481</v>
+        <v>1623.137096214732</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>1751.618587659427</v>
+        <v>1751.012968700278</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>1860.60975070106</v>
+        <v>1859.782688398613</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>1947.319583525936</v>
+        <v>1946.26167312298</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>2009.279249028172</v>
+        <v>2007.989274395331</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>2044.863961180243</v>
+        <v>2043.349243319098</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>2053.368988056273</v>
+        <v>2051.645252918456</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>2035.035472530622</v>
+        <v>2033.12624034096</v>
       </c>
     </row>
     <row r="28">
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>18131.28243364364</v>
+        <v>18121.66838433626</v>
       </c>
     </row>
     <row r="30">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>29659.11746810471</v>
+        <v>29582.27778281543</v>
       </c>
     </row>
     <row r="31">
@@ -13863,7 +13863,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>47790.39990174835</v>
+        <v>47703.94616715169</v>
       </c>
     </row>
     <row r="32">
@@ -13883,7 +13883,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>50246.39990174835</v>
+        <v>50159.94616715169</v>
       </c>
     </row>
     <row r="34">
@@ -13893,7 +13893,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.079166279653913</v>
+        <v>1.083142847089683</v>
       </c>
     </row>
     <row r="35">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>54224.22044797249</v>
+        <v>54330.38690135392</v>
       </c>
     </row>
     <row r="36">
@@ -13913,7 +13913,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>241.0000019286201</v>
+        <v>241.0000098675564</v>
       </c>
     </row>
     <row r="37">
@@ -13923,7 +13923,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>224.9967635437312</v>
+        <v>225.4372808167587</v>
       </c>
     </row>
     <row r="38">
@@ -13933,7 +13933,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>190.81</v>
+        <v>197.82</v>
       </c>
     </row>
     <row r="39">
@@ -13943,7 +13943,7 @@
         </is>
       </c>
       <c r="B39" s="22" t="n">
-        <v>0.1791665192795511</v>
+        <v>0.1396081327305565</v>
       </c>
     </row>
     <row r="40">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.08724060058593749</v>
+        <v>0.0967437744140625</v>
       </c>
     </row>
     <row r="41">
@@ -13963,7 +13963,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.6206082713072186</v>
+        <v>0.6201222364112385</v>
       </c>
     </row>
     <row r="42">
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>3.816988979982258</v>
+        <v>3.810863434208214</v>
       </c>
     </row>
     <row r="44">
@@ -14007,108 +14007,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.07746155185420442</v>
+        <v>0.07756998891341824</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>286.3172354121787</v>
+        <v>286.7844667636734</v>
       </c>
       <c r="C46" s="26" t="n">
-        <v>305.0015544485481</v>
+        <v>305.446790999656</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>327.6226008582165</v>
+        <v>328.0322450622926</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>355.571065937683</v>
+        <v>355.9231865443816</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>390.980104243864</v>
+        <v>391.2378569890648</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.08746155185420443</v>
+        <v>0.08756998891341825</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>240.4318091570776</v>
+        <v>240.8952456415113</v>
       </c>
       <c r="C47" s="26" t="n">
-        <v>252.7321599498754</v>
+        <v>253.188710082409</v>
       </c>
       <c r="D47" s="26" t="n">
-        <v>267.1731335410284</v>
+        <v>267.617569140003</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>284.366784679976</v>
+        <v>284.7911232899544</v>
       </c>
       <c r="F47" s="26" t="n">
-        <v>305.1830841452498</v>
+        <v>305.574843122561</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.09746155185420442</v>
+        <v>0.09756998891341824</v>
       </c>
       <c r="B48" s="26" t="n">
-        <v>206.7285768677158</v>
+        <v>207.1730428923861</v>
       </c>
       <c r="C48" s="26" t="n">
-        <v>215.2323984889111</v>
+        <v>215.6759679481848</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>224.9967635437312</v>
+        <v>225.4372808167587</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>236.3243886785459</v>
+        <v>236.7586567504037</v>
       </c>
       <c r="F48" s="26" t="n">
-        <v>249.6233537388046</v>
+        <v>250.0465739579531</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.1074615518542044</v>
+        <v>0.1075699889134182</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>181.0014979849219</v>
+        <v>181.4221587026437</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>187.1008709868786</v>
-      </c>
-      <c r="D49" s="26" t="n">
-        <v>193.9876504964452</v>
+        <v>187.5230180554713</v>
+      </c>
+      <c r="D49" s="28" t="n">
+        <v>194.410374794503</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>201.824834645899</v>
+        <v>202.2467955808295</v>
       </c>
       <c r="F49" s="26" t="n">
-        <v>210.8237448354521</v>
+        <v>211.2429650828718</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1174615518542044</v>
+        <v>0.1175699889134182</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>160.7734460714885</v>
+        <v>161.1696526673601</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>165.2756378290072</v>
+        <v>165.674189109235</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>170.2925919777793</v>
+        <v>170.6931182668985</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>175.91794531817</v>
+        <v>176.3198868131474</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>182.2695109801237</v>
+        <v>182.6720349327426</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($190.81); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($197.82); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -14143,14 +14143,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DOCU · DocuSign, Inc. — DCF</t>
+          <t>CRM · Salesforce, Inc. — DCF</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -14168,11 +14168,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0.9093333333333333</v>
+        <v>1.170666666666667</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Blume-adjusted from raw 0.86</t>
+          <t>Blume-adjusted from raw 1.26</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14209,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.09301333333333334</v>
+        <v>0.1073866666666667</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0</v>
+        <v>0.07111199756881965</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.09301333333333334</v>
+        <v>0.1031208949725051</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -14265,7 +14265,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0.08126026885982759</v>
+        <v>0.0951246618345723</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.0556301344299138</v>
+        <v>0.06256233091728615</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0.1330668176663952</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.25</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
@@ -14452,37 +14452,37 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>3199.269916666667</v>
+        <v>41222.49999999999</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>3442.843906641809</v>
+        <v>44875.31623522808</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>3687.314107278567</v>
+        <v>48559.56755791589</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>3930.242429253738</v>
+        <v>52230.052375883</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>4169.028872296059</v>
+        <v>55837.83264630832</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>4400.952508904081</v>
+        <v>59331.17761003071</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>4623.218687709506</v>
+        <v>62656.68208957172</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>4833.011478219721</v>
+        <v>65760.53112208677</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>5027.550116121548</v>
+        <v>68589.87352602693</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>5204.147976671059</v>
+        <v>71094.25896367359</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>5360.272415971191</v>
+        <v>73227.08673258382</v>
       </c>
     </row>
     <row r="21">
@@ -14492,31 +14492,31 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.07613424197384483</v>
+        <v>0.08861219565111507</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.07100821508786208</v>
+        <v>0.08209972946765784</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.06588218820187931</v>
+        <v>0.07558726328420061</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.06075616131589655</v>
+        <v>0.06907479710074338</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.0556301344299138</v>
+        <v>0.06256233091728615</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.05050410754393104</v>
+        <v>0.05604986473382892</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.04537808065794828</v>
+        <v>0.04953739855037169</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.04025205377196552</v>
+        <v>0.04302493236691446</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.03512602688598276</v>
+        <v>0.03651246618345723</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>0.03</v>
@@ -14529,37 +14529,37 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>0.1330668176663952</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.1447601358997557</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1564534541331161</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.1681467723664766</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.1798400905998371</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.1915334088331976</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.2032267270665581</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.2149200452999185</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.226613363533279</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.2383066817666395</v>
+        <v>0.260929508561263</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.25</v>
+        <v>0.260929508561263</v>
       </c>
     </row>
     <row r="23">
@@ -14569,37 +14569,37 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>425.7166666666666</v>
+        <v>10756.16666666666</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>498.386551807114</v>
+        <v>11709.29421178933</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>576.8930285574993</v>
+        <v>12670.62409883444</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>660.8575790967964</v>
+        <v>13628.36189856818</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>749.7585301070601</v>
+        <v>14569.73823152728</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>842.9294361434119</v>
+        <v>15481.25501614632</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>939.5616024161504</v>
+        <v>16348.97726571124</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>1038.711045834009</v>
+        <v>17158.86306841374</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>1139.310042146431</v>
+        <v>17897.12199142539</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>1240.183235743051</v>
+        <v>18550.59005291852</v>
       </c>
       <c r="L23" s="16" t="n">
-        <v>1340.068103992798</v>
+        <v>19107.10775450608</v>
       </c>
     </row>
     <row r="24">
@@ -14646,34 +14646,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9565050561883646</v>
+        <v>0.952112889388431</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8751083148010069</v>
+        <v>0.8631083807112203</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.800638279619346</v>
+        <v>0.7824241065914475</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.7325055012619663</v>
+        <v>0.7092822828008793</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6701706913565857</v>
+        <v>0.6429778331943915</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.613140453934614</v>
+        <v>0.5828715928823174</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5609633800758278</v>
+        <v>0.5283841467773532</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.513226474891274</v>
+        <v>0.478990244120544</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4695518885630617</v>
+        <v>0.4342137351432208</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.4295939255663807</v>
+        <v>0.3936229810550759</v>
       </c>
     </row>
     <row r="26">
@@ -14683,34 +14683,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>476.7092567397888</v>
+        <v>11148.56994468597</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>504.8438860414024</v>
+        <v>10936.12184854556</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>529.1078752014649</v>
+        <v>10663.15888279213</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>549.2022479215071</v>
+        <v>10334.05719266891</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>564.9066029850474</v>
+        <v>9954.103805411567</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>576.0832274049718</v>
+        <v>9529.354420861904</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>582.6788591931436</v>
+        <v>9066.471222073233</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>584.7240767390419</v>
+        <v>8572.546831728005</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>582.3303805073984</v>
+        <v>8054.92099598843</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>575.6851173205629</v>
+        <v>7520.99671366924</v>
       </c>
     </row>
     <row r="28">
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>5526.271530054329</v>
+        <v>95780.30185842495</v>
       </c>
     </row>
     <row r="30">
@@ -14737,7 +14737,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>9000.71567796544</v>
+        <v>100869.4307183998</v>
       </c>
     </row>
     <row r="31">
@@ -14747,7 +14747,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>14526.98720801977</v>
+        <v>196649.7325768248</v>
       </c>
     </row>
     <row r="32">
@@ -14757,7 +14757,7 @@
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>602.442</v>
+        <v>-4874</v>
       </c>
     </row>
     <row r="33">
@@ -14767,7 +14767,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>15129.42920801977</v>
+        <v>191775.7325768248</v>
       </c>
     </row>
     <row r="34">
@@ -14777,7 +14777,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.07316800473716</v>
+        <v>1.088605673247045</v>
       </c>
     </row>
     <row r="35">
@@ -14787,7 +14787,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>16236.41935598269</v>
+        <v>208768.1504742396</v>
       </c>
     </row>
     <row r="36">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>186.9024552980576</v>
+        <v>822.9999841515033</v>
       </c>
     </row>
     <row r="37">
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>86.87108647176464</v>
+        <v>253.667259410066</v>
       </c>
     </row>
     <row r="38">
@@ -14817,7 +14817,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>74.65000000000001</v>
+        <v>229.17</v>
       </c>
     </row>
     <row r="39">
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="B39" s="22" t="n">
-        <v>0.163711808061147</v>
+        <v>0.106895577126439</v>
       </c>
     </row>
     <row r="40">
@@ -14837,7 +14837,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.04027404785156251</v>
+        <v>0.0676849365234375</v>
       </c>
     </row>
     <row r="41">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.6195858472978144</v>
+        <v>0.5129395773726433</v>
       </c>
     </row>
     <row r="42">
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>4.086436732966567</v>
+        <v>3.675521120456186</v>
       </c>
     </row>
     <row r="44">
@@ -14891,108 +14891,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.07301333333333333</v>
+        <v>0.08312089497250505</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>111.5852893250758</v>
+        <v>315.4653560090225</v>
       </c>
       <c r="C46" s="26" t="n">
-        <v>119.6012678820436</v>
+        <v>332.2548603736144</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>129.4808496373145</v>
+        <v>352.2049862550845</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>141.9594094060731</v>
+        <v>376.3009464758513</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>158.2178237089871</v>
+        <v>405.9849076497826</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.08301333333333334</v>
+        <v>0.09312089497250506</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>92.85012105327739</v>
+        <v>270.4901396319864</v>
       </c>
       <c r="C47" s="26" t="n">
-        <v>97.98446643484104</v>
+        <v>281.8742767225211</v>
       </c>
       <c r="D47" s="26" t="n">
-        <v>104.0873125800296</v>
+        <v>295.0619587557399</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>111.4612319295757</v>
+        <v>310.5186495575706</v>
       </c>
       <c r="F47" s="26" t="n">
-        <v>120.5494846678879</v>
+        <v>328.8850599358187</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.09301333333333334</v>
+        <v>0.1031208949725051</v>
       </c>
       <c r="B48" s="26" t="n">
-        <v>79.35977430134015</v>
+        <v>236.4760665776023</v>
       </c>
       <c r="C48" s="26" t="n">
-        <v>82.8393333404919</v>
+        <v>244.5215159160737</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>86.87108647176464</v>
+        <v>253.667259410066</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>91.59780969001842</v>
+        <v>264.1555782618373</v>
       </c>
       <c r="F48" s="26" t="n">
-        <v>97.21614317328488</v>
+        <v>276.305521026948</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.1030133333333333</v>
+        <v>0.113120894972505</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>69.20923178351772</v>
+        <v>209.877349929983</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>71.66736851341174</v>
+        <v>215.7472224069135</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>74.46217481003706</v>
+        <v>222.3232798303455</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>77.66790146001836</v>
+        <v>229.7411168347393</v>
       </c>
       <c r="F49" s="26" t="n">
-        <v>81.38236594061453</v>
+        <v>238.1734158485468</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1130133333333333</v>
+        <v>0.1231208949725051</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>61.31368384088358</v>
+        <v>188.5252718603484</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>63.10656954121506</v>
+        <v>192.9175414182693</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>65.11543087200731</v>
+        <v>197.7814848748591</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>67.38179450977171</v>
+        <v>203.1973908890361</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>69.95856222502395</v>
+        <v>209.2648666458113</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($74.65); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($229.17); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -15027,14 +15027,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ZM · Zoom Communications, Inc. — DCF</t>
+          <t>DOCU · DocuSign, Inc. — DCF</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -15052,11 +15052,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>1.022</v>
+        <v>0.9093333333333333</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Blume-adjusted from raw 1.03</t>
+          <t>Blume-adjusted from raw 0.86</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.09920999999999999</v>
+        <v>0.09301333333333334</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.09920999999999999</v>
+        <v>0.09301333333333334</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0.0425252126851534</v>
+        <v>0.08126026885982759</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.0362626063425767</v>
+        <v>0.0556301344299138</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0.2348577061013407</v>
+        <v>0.1330668176663952</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
@@ -15336,37 +15336,37 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>4851.824333333333</v>
+        <v>3199.269916666667</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>5052.072181850735</v>
+        <v>3442.843906641809</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>5254.256970169</v>
+        <v>3687.314107278567</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>5457.95215951174</v>
+        <v>3930.242429253738</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>5662.707931271059</v>
+        <v>4169.028872296059</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>5868.052479815728</v>
+        <v>4400.952508904081</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>6073.493496353133</v>
+        <v>4623.218687709506</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>6278.519840578843</v>
+        <v>4833.011478219721</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>6482.603395066451</v>
+        <v>5027.550116121548</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>6685.201095546114</v>
+        <v>5204.147976671059</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>6885.757128412498</v>
+        <v>5360.272415971191</v>
       </c>
     </row>
     <row r="21">
@@ -15376,31 +15376,31 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.04127269141663806</v>
+        <v>0.07613424197384483</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.04002017014812272</v>
+        <v>0.07100821508786208</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.03876764887960738</v>
+        <v>0.06588218820187931</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.03751512761109204</v>
+        <v>0.06075616131589655</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.0362626063425767</v>
+        <v>0.0556301344299138</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.03501008507406136</v>
+        <v>0.05050410754393104</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.03375756380554602</v>
+        <v>0.04537808065794828</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.03250504253703068</v>
+        <v>0.04025205377196552</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.03125252126851534</v>
+        <v>0.03512602688598276</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>0.03</v>
@@ -15413,34 +15413,34 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>0.2348577061013407</v>
+        <v>0.1330668176663952</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.2363719354912066</v>
+        <v>0.1447601358997557</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.2378861648810726</v>
+        <v>0.1564534541331161</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.2394003942709385</v>
+        <v>0.1681467723664766</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.2409146236608044</v>
+        <v>0.1798400905998371</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.2424288530506704</v>
+        <v>0.1915334088331976</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.2439430824405363</v>
+        <v>0.2032267270665581</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.2454573118304022</v>
+        <v>0.2149200452999185</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.2469715412202682</v>
+        <v>0.226613363533279</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.2484857706101341</v>
+        <v>0.2383066817666395</v>
       </c>
       <c r="L22" s="7" t="n">
         <v>0.25</v>
@@ -15453,37 +15453,37 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>1139.488333333333</v>
+        <v>425.7166666666666</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>1194.168079865342</v>
+        <v>498.386551807114</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>1249.915039933147</v>
+        <v>576.8930285574993</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>1306.635898899031</v>
+        <v>660.8575790967964</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>1364.22915016322</v>
+        <v>749.7585301070601</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>1422.585232322869</v>
+        <v>842.9294361434119</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>1481.586724682933</v>
+        <v>939.5616024161504</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>1541.108602342328</v>
+        <v>1038.711045834009</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>1601.018551599304</v>
+        <v>1139.310042146431</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>1661.177345910489</v>
+        <v>1240.183235743051</v>
       </c>
       <c r="L23" s="16" t="n">
-        <v>1721.439282103124</v>
+        <v>1340.068103992798</v>
       </c>
     </row>
     <row r="24">
@@ -15530,34 +15530,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9538051535221719</v>
+        <v>0.9565050561883646</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8677187739578169</v>
+        <v>0.8751083148010069</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.7894021833478743</v>
+        <v>0.800638279619346</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.7181541137251974</v>
+        <v>0.7325055012619663</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6533365905743193</v>
+        <v>0.6701706913565857</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.5943692202348225</v>
+        <v>0.613140453934614</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5407239928992844</v>
+        <v>0.5609633800758278</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.491920554670431</v>
+        <v>0.513226474891274</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4475219063422194</v>
+        <v>0.4695518885630617</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.4071304903905709</v>
+        <v>0.4295939255663807</v>
       </c>
     </row>
     <row r="26">
@@ -15567,34 +15567,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>1139.003668747239</v>
+        <v>476.7092567397888</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>1084.574746002227</v>
+        <v>504.8438860414024</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>1031.461231431607</v>
+        <v>529.1078752014649</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>979.7267762535464</v>
+        <v>549.2022479215071</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>929.4269854871992</v>
+        <v>564.9066029850474</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>880.6095462600597</v>
+        <v>576.0832274049718</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>833.3143969499793</v>
+        <v>582.6788591931436</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>787.5739339403797</v>
+        <v>584.7240767390419</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>743.4132526143702</v>
+        <v>582.3303805073984</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>700.8504191002372</v>
+        <v>575.6851173205629</v>
       </c>
     </row>
     <row r="28">
@@ -15611,7 +15611,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>9109.954956786845</v>
+        <v>5526.271530054329</v>
       </c>
     </row>
     <row r="30">
@@ -15621,7 +15621,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>9948.403176326541</v>
+        <v>9000.71567796544</v>
       </c>
     </row>
     <row r="31">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>19058.35813311339</v>
+        <v>14526.98720801977</v>
       </c>
     </row>
     <row r="32">
@@ -15641,7 +15641,7 @@
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>7816.908</v>
+        <v>602.442</v>
       </c>
     </row>
     <row r="33">
@@ -15651,7 +15651,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>26875.26613311339</v>
+        <v>15129.42920801977</v>
       </c>
     </row>
     <row r="34">
@@ -15661,7 +15661,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.077995868827122</v>
+        <v>1.07683267871123</v>
       </c>
     </row>
     <row r="35">
@@ -15671,7 +15671,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>28971.42586512569</v>
+        <v>16291.86378144386</v>
       </c>
     </row>
     <row r="36">
@@ -15681,7 +15681,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>291.7837283788088</v>
+        <v>186.9024440063283</v>
       </c>
     </row>
     <row r="37">
@@ -15691,7 +15691,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>99.29075218174428</v>
+        <v>87.16774073265853</v>
       </c>
     </row>
     <row r="38">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>94.19</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="39">
@@ -15711,7 +15711,7 @@
         </is>
       </c>
       <c r="B39" s="22" t="n">
-        <v>0.05415386115027365</v>
+        <v>0.06082196340098012</v>
       </c>
     </row>
     <row r="40">
@@ -15721,7 +15721,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.0222564697265625</v>
+        <v>0.0652130126953125</v>
       </c>
     </row>
     <row r="41">
@@ -15731,7 +15731,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.5219968638873176</v>
+        <v>0.6195858472978144</v>
       </c>
     </row>
     <row r="42">
@@ -15741,7 +15741,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>3.720560612628233</v>
+        <v>4.086436732966567</v>
       </c>
     </row>
     <row r="44">
@@ -15775,108 +15775,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.07920999999999999</v>
+        <v>0.07301333333333333</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>116.6454807935026</v>
+        <v>111.9663396017075</v>
       </c>
       <c r="C46" s="26" t="n">
-        <v>121.6342064819916</v>
+        <v>120.0096917566207</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>127.6366947570463</v>
+        <v>129.9230110895205</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>134.9969048767185</v>
+        <v>142.4441836317066</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>144.234240760143</v>
+        <v>158.7581184544418</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.08921</v>
+        <v>0.08301333333333334</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>103.860805677994</v>
+        <v>93.16719299462949</v>
       </c>
       <c r="C47" s="26" t="n">
-        <v>107.1770127569811</v>
+        <v>98.31907154512426</v>
       </c>
       <c r="D47" s="26" t="n">
-        <v>111.0532953433128</v>
+        <v>104.4427581722969</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>115.6446272907091</v>
+        <v>111.8418585651955</v>
       </c>
       <c r="F47" s="26" t="n">
-        <v>121.1689671526343</v>
+        <v>120.9611465881853</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.09920999999999999</v>
-      </c>
-      <c r="B48" s="26" t="n">
-        <v>94.33884110421309</v>
+        <v>0.09301333333333334</v>
+      </c>
+      <c r="B48" s="28" t="n">
+        <v>79.63077833900373</v>
       </c>
       <c r="C48" s="26" t="n">
-        <v>96.64797576043148</v>
+        <v>83.12221965172796</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>99.29075218174428</v>
+        <v>87.16774073265853</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>102.3451119111575</v>
+        <v>91.91060513942176</v>
       </c>
       <c r="F48" s="26" t="n">
-        <v>105.9153236468894</v>
+        <v>97.54812455249093</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.10921</v>
+        <v>0.1030133333333333</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>86.97849388788087</v>
+        <v>69.4455729452971</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>88.64388616881104</v>
+        <v>71.91210391502855</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>90.51952870613941</v>
+        <v>74.71645413737114</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>92.64791919351876</v>
-      </c>
-      <c r="F49" s="26" t="n">
-        <v>95.08383612034031</v>
+        <v>77.93312795641182</v>
+      </c>
+      <c r="F49" s="28" t="n">
+        <v>81.66027688427189</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.11921</v>
+        <v>0.1130133333333333</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>81.12307643629478</v>
+        <v>61.52306266071001</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>82.35777530528897</v>
+        <v>63.32207084901651</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>83.73087781389687</v>
+        <v>65.33779219845854</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>85.26703726450783</v>
+        <v>67.61189519412883</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>86.99713175496366</v>
+        <v>70.19746225969554</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($94.19); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($82.17); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -15911,14 +15911,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRM · Salesforce, Inc. — DCF</t>
+          <t>ZM · Zoom Communications, Inc. — DCF</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -15936,11 +15936,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>1.170666666666667</v>
+        <v>1.022</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Blume-adjusted from raw 1.26</t>
+          <t>Blume-adjusted from raw 1.03</t>
         </is>
       </c>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.1073866666666667</v>
+        <v>0.09920999999999999</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.06793701587671259</v>
+        <v>0</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.1033113515409423</v>
+        <v>0.09920999999999999</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -16033,7 +16033,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0.0951246618345723</v>
+        <v>0.0425252126851534</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.06256233091728615</v>
+        <v>0.0362626063425767</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2348577061013407</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.25</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
@@ -16220,37 +16220,37 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>41222.49999999999</v>
+        <v>4851.824333333333</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>44875.31623522808</v>
+        <v>5052.072181850735</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>48559.56755791589</v>
+        <v>5254.256970169</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>52230.052375883</v>
+        <v>5457.95215951174</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>55837.83264630832</v>
+        <v>5662.707931271059</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>59331.17761003071</v>
+        <v>5868.052479815728</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>62656.68208957172</v>
+        <v>6073.493496353133</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>65760.53112208677</v>
+        <v>6278.519840578843</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>68589.87352602693</v>
+        <v>6482.603395066451</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>71094.25896367359</v>
+        <v>6685.201095546114</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>73227.08673258382</v>
+        <v>6885.757128412498</v>
       </c>
     </row>
     <row r="21">
@@ -16260,31 +16260,31 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.08861219565111507</v>
+        <v>0.04127269141663806</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.08209972946765784</v>
+        <v>0.04002017014812272</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.07558726328420061</v>
+        <v>0.03876764887960738</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.06907479710074338</v>
+        <v>0.03751512761109204</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.06256233091728615</v>
+        <v>0.0362626063425767</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.05604986473382892</v>
+        <v>0.03501008507406136</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.04953739855037169</v>
+        <v>0.03375756380554602</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.04302493236691446</v>
+        <v>0.03250504253703068</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.03651246618345723</v>
+        <v>0.03125252126851534</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>0.03</v>
@@ -16297,37 +16297,37 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2348577061013407</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2363719354912066</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2378861648810726</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2394003942709385</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2409146236608044</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2424288530506704</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2439430824405363</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2454573118304022</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2469715412202682</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.2484857706101341</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.260929508561263</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="23">
@@ -16337,37 +16337,37 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>10756.16666666666</v>
+        <v>1139.488333333333</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>11709.29421178933</v>
+        <v>1194.168079865342</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>12670.62409883444</v>
+        <v>1249.915039933147</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>13628.36189856818</v>
+        <v>1306.635898899031</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>14569.73823152728</v>
+        <v>1364.22915016322</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>15481.25501614632</v>
+        <v>1422.585232322869</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>16348.97726571124</v>
+        <v>1481.586724682933</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>17158.86306841374</v>
+        <v>1541.108602342328</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>17897.12199142539</v>
+        <v>1601.018551599304</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>18550.59005291852</v>
+        <v>1661.177345910489</v>
       </c>
       <c r="L23" s="16" t="n">
-        <v>19107.10775450608</v>
+        <v>1721.439282103124</v>
       </c>
     </row>
     <row r="24">
@@ -16414,34 +16414,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.952030707699743</v>
+        <v>0.9538051535221719</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8628849022264541</v>
+        <v>0.8677187739578169</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.7820864899298859</v>
+        <v>0.7894021833478743</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.7088538415177033</v>
+        <v>0.7181541137251974</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6424785175351281</v>
+        <v>0.6533365905743193</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.5823184150492143</v>
+        <v>0.5943692202348225</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5277915560606877</v>
+        <v>0.5407239928992844</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.4783704575535695</v>
+        <v>0.491920554670431</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4335770287194565</v>
+        <v>0.4475219063422194</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.3929779459931235</v>
+        <v>0.4071304903905709</v>
       </c>
     </row>
     <row r="26">
@@ -16451,34 +16451,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>11147.6076551143</v>
+        <v>1139.003668747239</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>10933.29023667091</v>
+        <v>1084.574746002227</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>10658.55772074538</v>
+        <v>1031.461231431607</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>10327.81491532546</v>
+        <v>979.7267762535464</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>9946.373772356956</v>
+        <v>929.4269854871992</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>9520.310529044607</v>
+        <v>880.6095462600597</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>9056.303039110355</v>
+        <v>833.3143969499793</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>8561.454435930216</v>
+        <v>787.5739339403797</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>8043.109716137118</v>
+        <v>743.4132526143702</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>7508.67195923508</v>
+        <v>700.8504191002372</v>
       </c>
     </row>
     <row r="28">
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>95703.49397967038</v>
+        <v>9109.954956786845</v>
       </c>
     </row>
     <row r="30">
@@ -16505,7 +16505,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>100433.8443208331</v>
+        <v>9948.403176326541</v>
       </c>
     </row>
     <row r="31">
@@ -16515,7 +16515,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>196137.3383005034</v>
+        <v>19058.35813311339</v>
       </c>
     </row>
     <row r="32">
@@ -16525,7 +16525,7 @@
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>-4874</v>
+        <v>7816.908</v>
       </c>
     </row>
     <row r="33">
@@ -16535,7 +16535,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>191263.3383005034</v>
+        <v>26875.26613311339</v>
       </c>
     </row>
     <row r="34">
@@ -16545,7 +16545,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.084357794193948</v>
+        <v>1.081911444926152</v>
       </c>
     </row>
     <row r="35">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>207397.8916297048</v>
+        <v>29076.65801485159</v>
       </c>
     </row>
     <row r="36">
@@ -16565,7 +16565,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>822.9999716825926</v>
+        <v>291.7837068062827</v>
       </c>
     </row>
     <row r="37">
@@ -16575,7 +16575,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>252.0023071272865</v>
+        <v>99.65141074225845</v>
       </c>
     </row>
     <row r="38">
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>240.7</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="39">
@@ -16595,7 +16595,7 @@
         </is>
       </c>
       <c r="B39" s="22" t="n">
-        <v>0.04695599138880979</v>
+        <v>0.04347026955244448</v>
       </c>
     </row>
     <row r="40">
@@ -16605,7 +16605,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.08268127441406249</v>
+        <v>0.0262115478515625</v>
       </c>
     </row>
     <row r="41">
@@ -16615,7 +16615,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.5120587706097941</v>
+        <v>0.5219968638873176</v>
       </c>
     </row>
     <row r="42">
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>3.66597243358701</v>
+        <v>3.720560612628233</v>
       </c>
     </row>
     <row r="44">
@@ -16659,108 +16659,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.08331135154094226</v>
+        <v>0.07920999999999999</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>313.2470827159257</v>
+        <v>117.0691777669777</v>
       </c>
       <c r="C46" s="26" t="n">
-        <v>329.8400250712202</v>
+        <v>122.0760242430131</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>349.5454269451131</v>
+        <v>128.1003156440711</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>373.3296635535699</v>
+        <v>135.4872606079108</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>402.6053558110092</v>
+        <v>144.7581497094295</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.09331135154094226</v>
+        <v>0.08921</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>268.7016101367699</v>
+        <v>104.2380642629738</v>
       </c>
       <c r="C47" s="26" t="n">
-        <v>279.9626610698108</v>
+        <v>107.5663169599585</v>
       </c>
       <c r="D47" s="26" t="n">
-        <v>293.002390021715</v>
+        <v>111.4566795534108</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>308.2783437578705</v>
+        <v>116.0646888160113</v>
       </c>
       <c r="F47" s="26" t="n">
-        <v>326.4197198280338</v>
+        <v>121.6090950025298</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.1033113515409423</v>
+        <v>0.09920999999999999</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>234.988184698278</v>
+        <v>94.68151260065761</v>
       </c>
       <c r="C48" s="26" t="n">
-        <v>242.9520895856911</v>
+        <v>96.99903483741947</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>252.0023071272865</v>
+        <v>99.65141074225845</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>262.3773729316441</v>
+        <v>102.7168649689848</v>
       </c>
       <c r="F48" s="26" t="n">
-        <v>274.3911757952869</v>
+        <v>106.3000449560095</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.1133113515409423</v>
+        <v>0.10921</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>208.6098560628625</v>
+        <v>87.29443004217522</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>214.4233469481253</v>
+        <v>88.96587160734923</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>220.9346408071409</v>
+        <v>90.84832713101004</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>228.2773969932511</v>
+        <v>92.98444867322102</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>236.6217383407001</v>
+        <v>95.42921369790723</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.1233113515409423</v>
+        <v>0.11921</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>187.4252846445294</v>
+        <v>81.41774367699048</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>191.7772427291733</v>
+        <v>82.65692740189496</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>196.5955918812249</v>
+        <v>84.0350174965903</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>201.9595502973152</v>
+        <v>85.57675681283834</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>207.9673535577008</v>
+        <v>87.31313560847637</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($240.70); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($95.50); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
@@ -16795,14 +16795,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PAYC · Paycom Software, Inc. — DCF</t>
+          <t>NOW · ServiceNow, Inc. — DCF</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Valuation date 2026-10-18 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
+          <t>Valuation date 2026-11-01 · $ in millions except per share · SBC treated as an expense · assumptions in config/config.yaml</t>
         </is>
       </c>
     </row>
@@ -16820,11 +16820,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0.8839999999999999</v>
+        <v>0.9933333333333332</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Blume-adjusted from raw 0.83</t>
+          <t>Blume-adjusted from raw 0.99</t>
         </is>
       </c>
     </row>
@@ -16861,7 +16861,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.09161999999999999</v>
+        <v>0.09763333333333332</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0</v>
+        <v>0.01348139782542052</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.09161999999999999</v>
+        <v>0.0969561177825697</v>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
     </row>
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0.0894753610875106</v>
+        <v>0.2088492352512745</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.0597376805437553</v>
+        <v>0.1194246176256372</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0.1410050202271287</v>
+        <v>0.1973941858713661</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
@@ -17104,37 +17104,37 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>2051.7</v>
+        <v>13278</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>2223.074038508921</v>
+        <v>15813.62413109978</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>2395.54076459586</v>
+        <v>18550.63652095141</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>2567.139943915669</v>
+        <v>21429.59262521752</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>2735.763087309073</v>
+        <v>24372.08015563395</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>2899.19122866214</v>
+        <v>27282.70650896191</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>3055.139143596574</v>
+        <v>30052.9841821159</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>3201.304969025869</v>
+        <v>32567.05967897639</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>3335.423871893457</v>
+        <v>34708.99021293918</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>3455.324141966337</v>
+        <v>36371.02755492018</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>3558.983866225327</v>
+        <v>37462.15838156779</v>
       </c>
     </row>
     <row r="21">
@@ -17144,31 +17144,31 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.08352782497875955</v>
+        <v>0.1909643117261471</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.07758028887000848</v>
+        <v>0.1730793882010196</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.07163275276125741</v>
+        <v>0.1551944646758922</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.06568521665250636</v>
+        <v>0.1373095411507647</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.0597376805437553</v>
+        <v>0.1194246176256372</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.05379014443500424</v>
+        <v>0.1015396941005098</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.04784260832625318</v>
+        <v>0.08365477057538234</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.04189507221750212</v>
+        <v>0.0657698470502549</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.03594753610875106</v>
+        <v>0.04788492352512744</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>0.03</v>
@@ -17181,34 +17181,34 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>0.1410050202271287</v>
+        <v>0.1973941858713661</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.1519045182044158</v>
+        <v>0.2026547672842295</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.162804016181703</v>
+        <v>0.2079153486970929</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.1737035141589901</v>
+        <v>0.2131759301099563</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.1846030121362772</v>
+        <v>0.2184365115228196</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.1955025101135643</v>
+        <v>0.223697092935683</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.2064020080908515</v>
+        <v>0.2289576743485464</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.2173015060681386</v>
+        <v>0.2342182557614098</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.2282010040454258</v>
+        <v>0.2394788371742732</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.2391005020227129</v>
+        <v>0.2447394185871366</v>
       </c>
       <c r="L22" s="7" t="n">
         <v>0.25</v>
@@ -17221,37 +17221,37 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>289.3</v>
+        <v>2620.999999999999</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>337.6949907524427</v>
+        <v>3204.706318208302</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>390.0036574031935</v>
+        <v>3856.962060806638</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>445.9212295960644</v>
+        <v>4568.273339758203</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>505.030106408496</v>
+        <v>5323.752167751219</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>566.7991625026771</v>
+        <v>6103.062133472217</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>630.5868542352971</v>
+        <v>6880.861365570909</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>695.6483911527372</v>
+        <v>7627.799913287589</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>761.1470764831683</v>
+        <v>8312.068615687906</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>826.1697369953507</v>
+        <v>8901.42413720789</v>
       </c>
       <c r="L23" s="16" t="n">
-        <v>889.7459665563317</v>
+        <v>9365.539595391947</v>
       </c>
     </row>
     <row r="24">
@@ -17298,34 +17298,34 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.9571152984789053</v>
+        <v>0.9547845278602765</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.8767843191576786</v>
+        <v>0.8703944600722183</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.8031955434653804</v>
+        <v>0.7934633354629244</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.7357830961922468</v>
+        <v>0.7233318841111552</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6740285962076975</v>
+        <v>0.6593991066600975</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>0.6174571702677649</v>
+        <v>0.6011171239858097</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.565633801384882</v>
+        <v>0.5479864820854744</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.5181599836801103</v>
+        <v>0.4995518719501705</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.4746706579946413</v>
+        <v>0.4553982277431337</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.4348314046963607</v>
+        <v>0.4151471698464052</v>
       </c>
     </row>
     <row r="26">
@@ -17335,34 +17335,34 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>323.2130418688553</v>
+        <v>3059.804008961359</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>341.9490912252636</v>
+        <v>3357.078410434824</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>358.1619443481616</v>
+        <v>3624.757401470897</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>371.5926153635431</v>
+        <v>3850.839686040336</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>382.0388438333781</v>
+        <v>4024.353718702649</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>389.3603746241781</v>
+        <v>4136.203594617056</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>393.482243915</v>
+        <v>4179.931240534353</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>394.3959567286822</v>
+        <v>4152.309436745155</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>392.1585326748428</v>
+        <v>4053.692776474426</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>386.8894884606109</v>
+        <v>3888.077257111413</v>
       </c>
     </row>
     <row r="28">
@@ -17379,7 +17379,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>3733.242133042515</v>
+        <v>38327.04753109247</v>
       </c>
     </row>
     <row r="30">
@@ -17389,7 +17389,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>6189.658936597183</v>
+        <v>57106.72026831952</v>
       </c>
     </row>
     <row r="31">
@@ -17399,7 +17399,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>9922.901069639698</v>
+        <v>95433.76779941199</v>
       </c>
     </row>
     <row r="32">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>370</v>
+        <v>4793</v>
       </c>
     </row>
     <row r="33">
@@ -17419,7 +17419,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>10292.9010696397</v>
+        <v>100226.767799412</v>
       </c>
     </row>
     <row r="34">
@@ -17429,7 +17429,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>1.072081673889996</v>
+        <v>1.080619670904252</v>
       </c>
     </row>
     <row r="35">
@@ -17439,7 +17439,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>11034.83060792346</v>
+        <v>108307.0168351974</v>
       </c>
     </row>
     <row r="36">
@@ -17449,7 +17449,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>45.07161799395963</v>
+        <v>1037.917048401826</v>
       </c>
     </row>
     <row r="37">
@@ -17459,7 +17459,7 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
-        <v>244.8288102149409</v>
+        <v>104.3503592141274</v>
       </c>
     </row>
     <row r="38">
@@ -17469,7 +17469,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>251.64</v>
+        <v>105.12</v>
       </c>
     </row>
     <row r="39">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>-0.02706719831926208</v>
+        <v>-0.00732154476667235</v>
       </c>
     </row>
     <row r="40">
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.09696350097656249</v>
+        <v>0.2110015869140625</v>
       </c>
     </row>
     <row r="41">
@@ -17499,7 +17499,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.6237751332153441</v>
+        <v>0.5983911312015848</v>
       </c>
     </row>
     <row r="42">
@@ -17509,7 +17509,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>4.178838039597534</v>
+        <v>3.845802422956988</v>
       </c>
     </row>
     <row r="44">
@@ -17543,108 +17543,108 @@
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>0.07161999999999999</v>
+        <v>0.07695611778256969</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>316.0147504029739</v>
+        <v>132.1663658693018</v>
       </c>
       <c r="C46" s="26" t="n">
-        <v>339.6088382892594</v>
+        <v>140.6202032778563</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>368.8718564701836</v>
+        <v>150.8744104375263</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>406.1258681467177</v>
+        <v>163.5726490523491</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>455.1616671972349</v>
+        <v>179.7069192031499</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>0.08162</v>
+        <v>0.0869561177825697</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>261.8022475716994</v>
+        <v>111.3834285152244</v>
       </c>
       <c r="C47" s="26" t="n">
-        <v>276.7713863481525</v>
+        <v>116.9326296870911</v>
       </c>
       <c r="D47" s="26" t="n">
-        <v>294.6403970301565</v>
+        <v>123.4561249976578</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>316.342314336357</v>
+        <v>131.2351982053004</v>
       </c>
       <c r="F47" s="26" t="n">
-        <v>343.2585318122357</v>
+        <v>140.6709401443028</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>0.09161999999999999</v>
+        <v>0.0969561177825697</v>
       </c>
       <c r="B48" s="28" t="n">
-        <v>223.0421136304078</v>
+        <v>96.12213113988295</v>
       </c>
       <c r="C48" s="28" t="n">
-        <v>233.117888499358</v>
+        <v>99.95036857860713</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>244.8288102149409</v>
+        <v>104.3503592141274</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>258.6080685104571</v>
+        <v>109.460528407149</v>
       </c>
       <c r="F48" s="26" t="n">
-        <v>275.0566910631443</v>
+        <v>115.4679092416889</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>0.10162</v>
+        <v>0.1069561177825697</v>
       </c>
       <c r="B49" s="28" t="n">
-        <v>194.0279524017</v>
+        <v>84.46740865024006</v>
       </c>
       <c r="C49" s="28" t="n">
-        <v>201.109622805756</v>
+        <v>87.20871687181712</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>209.180077125486</v>
+        <v>90.30624215586633</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>218.461947584473</v>
+        <v>93.83424164829475</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>229.2501261348242</v>
+        <v>97.88915333474927</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>0.11162</v>
+        <v>0.1169561177825697</v>
       </c>
       <c r="B50" s="28" t="n">
-        <v>171.5473935573239</v>
+        <v>75.2952865113551</v>
       </c>
       <c r="C50" s="28" t="n">
-        <v>176.6919166595518</v>
+        <v>77.31612770372703</v>
       </c>
       <c r="D50" s="28" t="n">
-        <v>182.4667415385781</v>
+        <v>79.56936671282594</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>188.9952632172684</v>
+        <v>82.09753809672043</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>196.4353349767589</v>
+        <v>84.95423065043761</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Green = above today's price ($251.64); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
+          <t>Green = above today's price ($105.12); red = below; underlined = base case; NM = WACC ≤ growth or negative equity.</t>
         </is>
       </c>
     </row>
